--- a/reports/devops-jobs-israel-2026-W39.xlsx
+++ b/reports/devops-jobs-israel-2026-W39.xlsx
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-21T12:39:14</t>
+    <t xml:space="preserve">2026-09-22T11:25:39</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -93,6 +93,9 @@
     <t xml:space="preserve">greenhouse</t>
   </si>
   <si>
+    <t xml:space="preserve">lever</t>
+  </si>
+  <si>
     <t xml:space="preserve">Title</t>
   </si>
   <si>
@@ -555,513 +558,507 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4468461559</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior DevOps Engineer - Data Platform (Cortex)</t>
+    <t xml:space="preserve">Principal DevOps Engineer (Cortex Agentix Endpoint Security)</t>
   </si>
   <si>
     <t xml:space="preserve">Palo Alto Networks</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-data-platform-cortex-at-palo-alto-networks-4455871961</t>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-cortex-agentix-endpoint-security-at-palo-alto-networks-4418753719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Checkmarx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4468561146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infinidat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-infinidat-4467985544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer (DevOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akamai Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-akamai-technologies-4461033122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Staff Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-at-palo-alto-networks-4428920772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4468397029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARAN Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aran-software-4470406189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-silverfort-4457951110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead - JB-760</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC | NEXT Technology Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-jb-760-at-pwc-next-technology-solutions-4467986877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethosia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check Point Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4467737639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cellebrite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cellebrite-4469980397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assured Allies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-assured-allies-4468548060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZyG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-zyg-4470271839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-jeen-ai-4469586887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4464714816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4464286063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-compie-technologies-4469572961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EasySend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-easysend-4467548799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CrowdStrike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-iii-at-crowdstrike-4438706386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth Startup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-stealth-startup-4468441366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bagira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AllCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4470273860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lod, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4468557198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluent Trade Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sela-4468591173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-jobgether-4468712370</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IgniteTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-25</t>
   </si>
   <si>
-    <t xml:space="preserve">Principal DevOps Engineer (Cortex Agentix Endpoint Security)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-cortex-agentix-endpoint-security-at-palo-alto-networks-4418753719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checkmarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infinidat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-infinidat-4467985544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer (DevOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akamai Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-akamai-technologies-4461033122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4468397029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-silverfort-4457951110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead - JB-760</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC | NEXT Technology Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-jb-760-at-pwc-next-technology-solutions-4467986877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethosia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4467737639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
+    <t xml:space="preserve">Site Reliability Engineering Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conifers.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineering-manager-at-conifers-ai-4467982436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4458308805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-calanit-by-one-4470276272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Centrical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-centrical-4468254008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-jobgether-4468496644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Haifa, Haifa District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4465531805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ScaleOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-scaleops-4467078972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-jeen-ai-4469586887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4464714816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4464286063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cust2Mate - A2Z (NASDAQ: AZ)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Givatayim, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cust2mate-a2z-nasdaq-az-4467084507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-compie-technologies-4469572961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EasySend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-easysend-4467548799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer III</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CrowdStrike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-iii-at-crowdstrike-4438706386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealth Startup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-stealth-startup-4468441366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bagira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yehud Monosson, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4468384015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE / DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">april</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-devops-lead-at-april-4416179005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fluent Trade Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DriveNets</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/it-devops-engineer-at-drivenets-4465793281</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-sqlink-group-4468564839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-cyera-4456176236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Center for Educational Technology (CET)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-the-center-for-educational-technology-cet-4467956789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4465561954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Database Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HR Home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/database-reliability-engineer-at-hr-home-4467191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fiverr-4458388230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops and Infra Group Tech lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sunbit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-and-infra-group-tech-lead-at-sunbit-4467977092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Millennium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4457617255</t>
   </si>
   <si>
     <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-10</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior DevSecOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devsecops-engineer-at-dream-4401076382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zadara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-leader-at-zadara-4448858731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-jobgether-4468712370</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/staff-site-reliability-engineer-at-jobgether-4466822711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IgniteTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineering Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conifers.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineering-manager-at-conifers-ai-4467982436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4458308805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Centrical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-centrical-4468254008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-sunbit-4467974106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infra-engineer-at-scaleops-4467093965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-cyera-4456176236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Center for Educational Technology (CET)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-the-center-for-educational-technology-cet-4467956789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4465561954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Database Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HR Home</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/database-reliability-engineer-at-hr-home-4467191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiverr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fiverr-4458388230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops and Infra Group Tech lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-and-infra-group-tech-lead-at-sunbit-4467977092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-jobgether-4468496644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Millennium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4457617255</t>
-  </si>
-  <si>
     <t xml:space="preserve">Sr Staff DevOps Platform Engineer</t>
   </si>
   <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-staff-devops-platform-engineer-at-palo-alto-networks-4419603015</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior Staff Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-at-palo-alto-networks-4428920772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cloud Engineer - Azure &amp; AWS</t>
   </si>
   <si>
@@ -1119,12 +1116,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-experis-israel-4465531772</t>
   </si>
   <si>
-    <t xml:space="preserve">Credo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-credo-4466110440</t>
-  </si>
-  <si>
     <t xml:space="preserve">Senior Network &amp; Infrastructure Engineer</t>
   </si>
   <si>
@@ -1164,7 +1155,7 @@
     <t xml:space="preserve">COMDA</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4465988466</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4468579109</t>
   </si>
   <si>
     <t xml:space="preserve">System Administrator</t>
@@ -1176,6 +1167,18 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-talent-integration-4466204750</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mendix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boston, MA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://jobs.lever.co/mendix/f61ca692-a66b-4e9f-a864-ad29e7cd716e</t>
+  </si>
+  <si>
     <t xml:space="preserve">Skill</t>
   </si>
   <si>
@@ -1239,10 +1242,10 @@
     <t xml:space="preserve">0%</t>
   </si>
   <si>
-    <t xml:space="preserve">41.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.4%</t>
+    <t xml:space="preserve">44.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.0%</t>
   </si>
   <si>
     <t xml:space="preserve">Role</t>
@@ -1564,9 +1567,6 @@
   </si>
   <si>
     <t xml:space="preserve">indeed_il</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lever</t>
   </si>
   <si>
     <t xml:space="preserve">alljobs</t>
@@ -1700,7 +1700,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -1708,7 +1708,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -1716,7 +1716,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
@@ -1724,7 +1724,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>934</v>
+        <v>929</v>
       </c>
     </row>
     <row r="10">
@@ -1796,7 +1796,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20">
@@ -1805,6 +1805,14 @@
       </c>
       <c r="B20" s="3">
         <v>30</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1820,15 +1828,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B2" s="3">
         <v>16</v>
@@ -1836,7 +1844,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B3" s="3">
         <v>7</v>
@@ -1844,7 +1852,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B4" s="3">
         <v>7</v>
@@ -1852,7 +1860,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1860,7 +1868,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1868,7 +1876,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1887,15 +1895,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B2" s="3">
         <v>19</v>
@@ -1903,7 +1911,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B3" s="3">
         <v>19</v>
@@ -1911,7 +1919,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B4" s="3">
         <v>17</v>
@@ -1919,7 +1927,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B5" s="3">
         <v>15</v>
@@ -1927,7 +1935,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B6" s="3">
         <v>14</v>
@@ -1935,7 +1943,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B7" s="3">
         <v>13</v>
@@ -1943,7 +1951,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B8" s="3">
         <v>11</v>
@@ -1951,7 +1959,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
@@ -1959,7 +1967,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
@@ -1967,7 +1975,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
@@ -1975,7 +1983,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -1983,7 +1991,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B13" s="3">
         <v>7</v>
@@ -1991,7 +1999,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -1999,7 +2007,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -2007,7 +2015,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -2035,13 +2043,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="2">
@@ -2052,10 +2060,10 @@
         <v>30</v>
       </c>
       <c r="C2" s="3">
-        <v>15.7</v>
+        <v>12.9</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2064,43 +2072,43 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C3" s="3">
-        <v>38.1</v>
+        <v>38.3</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.8</v>
+        <v>8.1</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>515</v>
+        <v>24</v>
       </c>
       <c r="B5" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C5" s="3">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E5" s="3"/>
     </row>
@@ -2112,10 +2120,10 @@
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>31.4</v>
+        <v>36.1</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E6" s="3"/>
     </row>
@@ -2127,10 +2135,10 @@
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>14.0</v>
+        <v>17.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E7" s="3"/>
     </row>
@@ -2142,10 +2150,10 @@
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>29.2</v>
+        <v>22.4</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2170,1403 +2178,1403 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J2" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J3" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J4" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J5" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J6" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J7" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J8" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J9" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J10" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J11" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J12" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J13" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J14" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J15" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J16" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J17" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J18" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J19" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J20" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J21" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J22" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J23" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J24" s="3">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J25" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J26" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J27" s="3">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J28" s="3">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J29" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J30" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J31" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J32" s="3">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J33" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J34" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J35" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F36" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>181</v>
+      </c>
       <c r="G36" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>181</v>
+        <v>89</v>
       </c>
       <c r="J36" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>183</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>88</v>
+        <v>187</v>
       </c>
       <c r="J37" s="3">
-        <v>25</v>
+        <v>70</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>35</v>
+        <v>190</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="J38" s="3">
-        <v>69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J39" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="J40" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J41" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>198</v>
+        <v>180</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>98</v>
+        <v>202</v>
       </c>
       <c r="J42" s="3">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>40</v>
+        <v>203</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="J43" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>202</v>
+        <v>183</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>98</v>
+        <v>192</v>
       </c>
       <c r="J44" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>205</v>
+        <v>41</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>207</v>
+        <v>165</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>208</v>
+        <v>36</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
@@ -3576,27 +3584,27 @@
         <v>209</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>210</v>
+        <v>89</v>
       </c>
       <c r="J45" s="3">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>40</v>
+        <v>210</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>211</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>207</v>
+        <v>165</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>208</v>
+        <v>36</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
@@ -3606,27 +3614,27 @@
         <v>212</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>213</v>
+        <v>99</v>
       </c>
       <c r="J46" s="3">
-        <v>87</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>214</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>35</v>
+        <v>190</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
@@ -3636,57 +3644,57 @@
         <v>215</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>77</v>
+        <v>216</v>
       </c>
       <c r="J47" s="3">
-        <v>5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>185</v>
+        <v>41</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>217</v>
+        <v>189</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="I48" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="J48" s="3">
-        <v>5</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>220</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
@@ -3696,7 +3704,7 @@
         <v>221</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="J49" s="3">
         <v>6</v>
@@ -3704,29 +3712,29 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B50" s="3" t="s">
-        <v>168</v>
-      </c>
       <c r="C50" s="3" t="s">
-        <v>169</v>
+        <v>223</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>135</v>
+        <v>224</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="J50" s="3">
         <v>0</v>
@@ -3734,79 +3742,79 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C51" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="B51" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>169</v>
-      </c>
       <c r="D51" s="3" t="s">
-        <v>135</v>
+        <v>36</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>226</v>
+        <v>192</v>
       </c>
       <c r="J51" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>185</v>
+        <v>228</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>228</v>
+        <v>165</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>226</v>
+        <v>192</v>
       </c>
       <c r="J52" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>40</v>
+        <v>231</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>230</v>
+        <v>169</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>231</v>
+        <v>170</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
@@ -3816,27 +3824,27 @@
         <v>232</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>60</v>
+        <v>172</v>
       </c>
       <c r="J53" s="3">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>233</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>207</v>
+        <v>170</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>208</v>
+        <v>136</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
@@ -3849,54 +3857,54 @@
         <v>235</v>
       </c>
       <c r="J54" s="3">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>40</v>
+        <v>183</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>236</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>164</v>
+        <v>237</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>132</v>
+        <v>235</v>
       </c>
       <c r="J55" s="3">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>238</v>
+        <v>183</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>239</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>35</v>
+        <v>190</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
@@ -3909,84 +3917,84 @@
         <v>241</v>
       </c>
       <c r="J56" s="3">
-        <v>66</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="B57" s="3" t="s">
-        <v>243</v>
-      </c>
       <c r="C57" s="3" t="s">
-        <v>244</v>
+        <v>165</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>218</v>
+        <v>36</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>246</v>
+        <v>133</v>
       </c>
       <c r="J57" s="3">
-        <v>18</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>40</v>
+        <v>244</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>135</v>
+        <v>36</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="J58" s="3">
-        <v>1</v>
+        <v>67</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="C59" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="D59" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="E59" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
@@ -3999,84 +4007,84 @@
         <v>253</v>
       </c>
       <c r="J59" s="3">
-        <v>90</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="B60" s="3" t="s">
-        <v>255</v>
-      </c>
       <c r="C60" s="3" t="s">
-        <v>256</v>
+        <v>170</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>51</v>
+        <v>241</v>
       </c>
       <c r="J60" s="3">
-        <v>26</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>185</v>
+        <v>256</v>
       </c>
       <c r="B61" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C61" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="C61" s="3" t="s">
-        <v>259</v>
-      </c>
       <c r="D61" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>98</v>
+        <v>192</v>
       </c>
       <c r="J61" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="C62" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="C62" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="D62" s="3" t="s">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
@@ -4086,312 +4094,310 @@
         <v>263</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="J62" s="3">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="C63" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="D63" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="D63" s="3" t="s">
-        <v>267</v>
-      </c>
       <c r="E63" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>88</v>
+        <v>192</v>
       </c>
       <c r="J63" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>244</v>
+        <v>269</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>218</v>
+        <v>136</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>132</v>
+        <v>192</v>
       </c>
       <c r="J64" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="J65" s="3">
-        <v>6</v>
+        <v>42</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>135</v>
+        <v>277</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>277</v>
+        <v>89</v>
       </c>
       <c r="J66" s="3">
-        <v>42</v>
+        <v>26</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>278</v>
+        <v>183</v>
       </c>
       <c r="B67" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H67" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="C67" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="G67" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>280</v>
-      </c>
       <c r="I67" s="3" t="s">
-        <v>171</v>
+        <v>133</v>
       </c>
       <c r="J67" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>282</v>
+        <v>188</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>164</v>
+        <v>237</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>284</v>
+        <v>192</v>
       </c>
       <c r="J68" s="3">
-        <v>85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>164</v>
+        <v>284</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>288</v>
+        <v>172</v>
       </c>
       <c r="J69" s="3">
-        <v>46</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>291</v>
+        <v>165</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>135</v>
+        <v>36</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>171</v>
+        <v>289</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>39</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>164</v>
+        <v>284</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="J71" s="3">
-        <v>38</v>
+        <v>65</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="I72" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="J72" s="3">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="73">
@@ -4402,13 +4408,13 @@
         <v>300</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>291</v>
+        <v>237</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>135</v>
+        <v>36</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
@@ -4418,117 +4424,117 @@
         <v>301</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>302</v>
+        <v>78</v>
       </c>
       <c r="J73" s="3">
-        <v>64</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>303</v>
+        <v>282</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>181</v>
+        <v>89</v>
       </c>
       <c r="J74" s="3">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>228</v>
+        <v>165</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>77</v>
+        <v>306</v>
       </c>
       <c r="J75" s="3">
-        <v>5</v>
+        <v>86</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>274</v>
+        <v>308</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>275</v>
+        <v>309</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>88</v>
+        <v>192</v>
       </c>
       <c r="J76" s="3">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>312</v>
+        <v>266</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
@@ -4538,27 +4544,27 @@
         <v>313</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J77" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>40</v>
+        <v>314</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>314</v>
+        <v>283</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>228</v>
+        <v>284</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
@@ -4568,10 +4574,10 @@
         <v>315</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>77</v>
+        <v>172</v>
       </c>
       <c r="J78" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4579,662 +4585,662 @@
         <v>316</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>164</v>
+        <v>317</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>35</v>
+        <v>251</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>60</v>
+        <v>192</v>
       </c>
       <c r="J79" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J80" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J81" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J82" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J83" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J84" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J85" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>290</v>
+        <v>336</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>291</v>
+        <v>165</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>135</v>
+        <v>36</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>171</v>
+        <v>241</v>
       </c>
       <c r="J86" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>279</v>
+        <v>339</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>235</v>
+        <v>52</v>
       </c>
       <c r="J87" s="3">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>338</v>
+        <v>295</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>164</v>
+        <v>296</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>51</v>
+        <v>343</v>
       </c>
       <c r="J88" s="3">
-        <v>26</v>
+        <v>43</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>341</v>
+        <v>223</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>342</v>
+        <v>224</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="I89" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>277</v>
-      </c>
       <c r="J89" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>179</v>
+        <v>249</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>164</v>
+        <v>250</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>35</v>
+        <v>251</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F90" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>347</v>
+      </c>
       <c r="G90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>346</v>
+        <v>202</v>
       </c>
       <c r="J90" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>347</v>
+        <v>41</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>243</v>
+        <v>349</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>244</v>
+        <v>223</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>348</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>346</v>
+        <v>125</v>
       </c>
       <c r="J91" s="3">
-        <v>22</v>
+        <v>36</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="J92" s="3">
         <v>40</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F92" s="3"/>
-      <c r="G92" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H92" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="I92" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="J92" s="3">
-        <v>35</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>164</v>
+        <v>357</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F93" s="3" t="s">
-        <v>354</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>210</v>
+        <v>133</v>
       </c>
       <c r="J93" s="3">
-        <v>39</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>356</v>
+        <v>213</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>358</v>
+        <v>165</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>135</v>
+        <v>36</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>132</v>
+        <v>361</v>
       </c>
       <c r="J94" s="3">
-        <v>3</v>
+        <v>77</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>205</v>
+        <v>362</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>164</v>
+        <v>49</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>362</v>
+        <v>78</v>
       </c>
       <c r="J95" s="3">
-        <v>76</v>
+        <v>6</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="J96" s="3">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>333</v>
+        <v>368</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>291</v>
+        <v>262</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="J97" s="3">
-        <v>6</v>
+        <v>32</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>48</v>
+        <v>373</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F98" s="3"/>
+        <v>37</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>374</v>
+      </c>
       <c r="G98" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="J98" s="3">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>135</v>
+        <v>36</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F99" s="3"/>
       <c r="G99" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>129</v>
+        <v>192</v>
       </c>
       <c r="J99" s="3">
-        <v>31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>376</v>
+        <v>185</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>135</v>
+        <v>36</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>377</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F100" s="3"/>
       <c r="G100" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="J100" s="3">
         <v>5</v>
@@ -5242,66 +5248,36 @@
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>228</v>
+        <v>384</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>35</v>
+        <v>136</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>98</v>
+        <v>192</v>
       </c>
       <c r="J101" s="3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F102" s="3"/>
-      <c r="G102" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="J102" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J102"/>
+  <autoFilter ref="A1:J101"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5403,7 +5379,6 @@
     <hyperlink ref="H99" r:id="rId98"/>
     <hyperlink ref="H100" r:id="rId99"/>
     <hyperlink ref="H101" r:id="rId100"/>
-    <hyperlink ref="H102" r:id="rId101"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5411,9 +5386,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="42" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -5422,36 +5397,36 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5459,18 +5434,18 @@
         <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5478,18 +5453,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>177</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>168</v>
-      </c>
       <c r="C4" s="3" t="s">
-        <v>169</v>
+        <v>223</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5497,18 +5472,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>278</v>
+        <v>41</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5516,18 +5491,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>280</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>289</v>
+        <v>228</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>290</v>
+        <v>229</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>291</v>
+        <v>165</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5535,18 +5510,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>292</v>
+        <v>230</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>333</v>
+        <v>256</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>290</v>
+        <v>257</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>291</v>
+        <v>258</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5554,11 +5529,144 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>334</v>
+        <v>259</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>385</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G7"/>
+  <autoFilter ref="A1:G14"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5566,6 +5674,13 @@
     <hyperlink ref="G5" r:id="rId4"/>
     <hyperlink ref="G6" r:id="rId5"/>
     <hyperlink ref="G7" r:id="rId6"/>
+    <hyperlink ref="G8" r:id="rId7"/>
+    <hyperlink ref="G9" r:id="rId8"/>
+    <hyperlink ref="G10" r:id="rId9"/>
+    <hyperlink ref="G11" r:id="rId10"/>
+    <hyperlink ref="G12" r:id="rId11"/>
+    <hyperlink ref="G13" r:id="rId12"/>
+    <hyperlink ref="G14" r:id="rId13"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5579,23 +5694,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>183</v>
+        <v>388</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>387</v>
+        <v>181</v>
       </c>
       <c r="B3" s="3">
         <v>21</v>
@@ -5603,7 +5718,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B4" s="3">
         <v>19</v>
@@ -5611,7 +5726,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B5" s="3">
         <v>18</v>
@@ -5619,7 +5734,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B6" s="3">
         <v>14</v>
@@ -5627,7 +5742,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B7" s="3">
         <v>14</v>
@@ -5635,7 +5750,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B8" s="3">
         <v>13</v>
@@ -5643,7 +5758,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B9" s="3">
         <v>13</v>
@@ -5651,7 +5766,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B10" s="3">
         <v>12</v>
@@ -5659,7 +5774,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
@@ -5667,7 +5782,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B12" s="3">
         <v>10</v>
@@ -5675,7 +5790,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B13" s="3">
         <v>8</v>
@@ -5683,7 +5798,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B14" s="3">
         <v>8</v>
@@ -5691,7 +5806,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B15" s="3">
         <v>8</v>
@@ -5699,7 +5814,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -5718,15 +5833,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B2" s="3">
         <v>7</v>
@@ -5734,7 +5849,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B3" s="3">
         <v>5</v>
@@ -5742,15 +5857,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>179</v>
+        <v>35</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5758,7 +5873,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>53</v>
+        <v>115</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5766,7 +5881,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>114</v>
+        <v>180</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5774,7 +5889,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -5782,7 +5897,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="B9" s="3">
         <v>3</v>
@@ -5790,15 +5905,15 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>290</v>
+        <v>127</v>
       </c>
       <c r="B10" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>126</v>
+        <v>169</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5806,7 +5921,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5814,7 +5929,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>220</v>
+        <v>268</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5822,7 +5937,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5830,15 +5945,15 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>314</v>
+        <v>48</v>
       </c>
       <c r="B15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>47</v>
+        <v>134</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -5859,16 +5974,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>400</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>401</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="2">
@@ -5876,7 +5991,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C2" s="3">
         <v>26.9</v>
@@ -5890,7 +6005,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C3" s="3">
         <v>23.8</v>
@@ -5904,7 +6019,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3">
         <v>10.9</v>
@@ -5918,7 +6033,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C5" s="3">
         <v>10.1</v>
@@ -5932,7 +6047,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C6" s="3">
         <v>10.1</v>
@@ -5946,13 +6061,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>179</v>
+        <v>249</v>
       </c>
       <c r="C7" s="3">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="D7" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -5960,10 +6075,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>243</v>
+        <v>180</v>
       </c>
       <c r="C8" s="3">
-        <v>4.3</v>
+        <v>4.0</v>
       </c>
       <c r="D8" s="3">
         <v>3</v>
@@ -5974,7 +6089,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C9" s="3">
         <v>3.6</v>
@@ -5988,7 +6103,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="C10" s="3">
         <v>3.6</v>
@@ -6002,13 +6117,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>290</v>
+        <v>48</v>
       </c>
       <c r="C11" s="3">
-        <v>3.6</v>
+        <v>3.0</v>
       </c>
       <c r="D11" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -6016,13 +6131,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>279</v>
+        <v>141</v>
       </c>
       <c r="C12" s="3">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
       <c r="D12" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -6030,10 +6145,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>47</v>
+        <v>146</v>
       </c>
       <c r="C13" s="3">
-        <v>3.0</v>
+        <v>2.4</v>
       </c>
       <c r="D13" s="3">
         <v>1</v>
@@ -6044,13 +6159,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="C14" s="3">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D14" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -6058,13 +6173,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>145</v>
+        <v>188</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
       </c>
       <c r="D15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -6072,7 +6187,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>168</v>
+        <v>268</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -6095,46 +6210,46 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B3" s="3">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" s="3">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
   </sheetData>
@@ -6150,31 +6265,31 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B2" s="3">
-        <v>68</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B3" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>218</v>
+        <v>190</v>
       </c>
       <c r="B4" s="3">
         <v>4</v>
@@ -6182,31 +6297,31 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>208</v>
+        <v>251</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>342</v>
+        <v>224</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>312</v>
+        <v>277</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -6233,34 +6348,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2">
@@ -6268,31 +6383,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3">
@@ -6300,31 +6415,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>311</v>
+        <v>265</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4">
@@ -6332,31 +6447,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="5">
@@ -6364,31 +6479,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6">
@@ -6396,31 +6511,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F6" s="3">
         <v>80</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="7">
@@ -6428,31 +6543,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>217</v>
+        <v>317</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F7" s="3">
         <v>70</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8">
@@ -6460,31 +6575,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F8" s="3">
         <v>68</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9">
@@ -6492,31 +6607,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F9" s="3">
         <v>61</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10">
@@ -6524,31 +6639,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>341</v>
+        <v>223</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F10" s="3">
         <v>60</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11">
@@ -6556,31 +6671,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F11" s="3">
         <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>346</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6588,31 +6703,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F12" s="3">
         <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
@@ -6620,31 +6735,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F13" s="3">
         <v>46</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14">
@@ -6652,31 +6767,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F14" s="3">
         <v>44</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15">
@@ -6684,31 +6799,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="F15" s="3">
         <v>39</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16">
@@ -6716,31 +6831,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F16" s="3">
         <v>36</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="17">
@@ -6748,31 +6863,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F17" s="3">
         <v>32</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18">
@@ -6780,31 +6895,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F18" s="3">
         <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -6812,31 +6927,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>207</v>
+        <v>189</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F19" s="3">
         <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
     </row>
     <row r="20">
@@ -6844,31 +6959,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F20" s="3">
         <v>27</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21">
@@ -6876,31 +6991,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F21" s="3">
         <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W39.xlsx
+++ b/reports/devops-jobs-israel-2026-W39.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="518">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-22T11:25:39</t>
+    <t xml:space="preserve">2026-09-23T11:23:07</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -180,1041 +180,1041 @@
     <t xml:space="preserve">2026-08-26</t>
   </si>
   <si>
+    <t xml:space="preserve">Cloud Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jfrog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, Python, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=8188177&amp;gh_jid=8188177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-15</t>
+  </si>
+  <si>
     <t xml:space="preserve">Developer Advocate</t>
   </si>
   <si>
-    <t xml:space="preserve">Jfrog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">CI/CD, Security</t>
   </si>
   <si>
     <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, Python, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=8188177&amp;gh_jid=8188177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, CI/CD, Python, Helm, Prometheus, Istio, MongoDB, Kafka, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7510102&amp;gh_jid=7510102</t>
+    <t xml:space="preserve">Developer Experience (DevEx) Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Python, Security, Observability, Backstage/IDP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4693375006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of Quality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4695788006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668069006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cyber Defense Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4677810006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4700779006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevSecOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4704221006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Director of Platform Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE Engineer /Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Terraform, Ansible, Docker, CI/CD, Linux, Python, Prometheus, Grafana, ELK/Elastic, Networking, Argo CD, Rust, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8070135?gh_jid=8070135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer, Traffic Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Linux, Istio, Service Mesh, Nginx, Networking, Observability, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8200807?gh_jid=8200807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Developer – Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Docker, Linux, Prometheus, Grafana, MySQL, Redis, Kafka, Observability, Airflow, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8176684?gh_jid=8176684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CloudFormation, Security, ECS/Fargate, Databricks, Airflow, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7556162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yotpo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8143530?gh_jid=8143530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff Engineer - Office of the CTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8211515?gh_jid=8211515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riskified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel (other)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevEx/DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axonius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Ansible, Docker, CI/CD, Linux, Python, Security, Observability, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7824320003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead (FedRAMP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orcasecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Helm, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://orca.security/about/careers/6149333004?gh_jid=6149333004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4954650101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer- Edge Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saltsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Terraform, Docker, CI/CD, Helm, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://salt.security/job-board?gh_jid=5208152007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-viz-ai-4449757750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-radware-4468903264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CommBox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commbox-4470453217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform DevOps Engineer - Core Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeen.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-core-platform-at-jeen-ai-4469586881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IVIX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-ivix-4468275010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer (Cortex Agentix Endpoint Security)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-cortex-agentix-endpoint-security-at-palo-alto-networks-4418753719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nayax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nayax-4469432294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4468561146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infinidat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-infinidat-4467985544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer (DevOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akamai Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-akamai-technologies-4461033122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4468397029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Secrets Manager)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-secrets-manager-at-palo-alto-networks-4419602029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireArc Technologies .LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-firearc-technologies-ltd-4470443498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARAN Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aran-software-4470406189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akeyless Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4457183616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-silverfort-4457951110</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead - JB-760</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PwC | NEXT Technology Solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-jb-760-at-pwc-next-technology-solutions-4467986877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethosia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer 4218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank Hapoalim בנק הפועלים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-4218-at-bank-hapoalim-%D7%91%D7%A0%D7%A7-%D7%94%D7%A4%D7%95%D7%A2%D7%9C%D7%99%D7%9D-4469435452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cellebrite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cellebrite-4469980397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assured Allies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-assured-allies-4468548060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZyG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-zyg-4470271839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-jeen-ai-4469586887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4464714816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4464286063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-compie-technologies-4469572961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EasySend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-easysend-4467548799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CrowdStrike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-iii-at-crowdstrike-4438706386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth Startup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-stealth-startup-4468441366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bagira</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rehovot, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AllCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4470273860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-confidential-careers-4468585946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lod, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4468557198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yael Korentec Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-yael-korentec-technologies-4470914031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-jobgether-4468712370</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IgniteTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VP, Site Reliability Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/vp-site-reliability-engineering-at-oracle-4459580128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4458308805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director, Site Reliability Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DuckDuckGo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-site-reliability-engineering-at-duckduckgo-4469057695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manager, Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crusoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-production-engineering-at-crusoe-4442593613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARMAN International</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Centrical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-centrical-4468254008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-jobgether-4468496644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-sqlink-group-4468564839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-cyera-4456176236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fluent Trade Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Database Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HR Home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/database-reliability-engineer-at-hr-home-4467191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fiverr-4458388230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr Staff DevOps Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-staff-devops-platform-engineer-at-palo-alto-networks-4419603015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer 4210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-4210-at-bank-hapoalim-%D7%91%D7%A0%D7%A7-%D7%94%D7%A4%D7%95%D7%A2%D7%9C%D7%99%D7%9D-4469434426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer - Azure &amp; AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-azure-aws-at-elbit-systems-israel-4458838595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior MLOps Platform Engineer - QuantumBlack, AI by McKinsey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuantumBlack, AI by McKinsey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-mlops-platform-engineer-quantumblack-ai-by-mckinsey-at-quantumblack-ai-by-mckinsey-4423517900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI SW Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Camtek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-sw-infrastructure-engineer-at-camtek-4431013854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Network &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wayve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-infrastructure-engineer-at-wayve-4456949923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-10</t>
   </si>
   <si>
-    <t xml:space="preserve">Developer Experience (DevEx) Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Python, Security, Observability, Backstage/IDP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4693375006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668069006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cyber Defense Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4677810006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4700779006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevSecOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4704221006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Director of Platform Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE Engineer /Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Terraform, Ansible, Docker, CI/CD, Linux, Python, Prometheus, Grafana, ELK/Elastic, Networking, Argo CD, Rust, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8070135?gh_jid=8070135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer, Traffic Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Linux, Istio, Service Mesh, Nginx, Networking, Observability, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8200807?gh_jid=8200807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Developer – Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Docker, Linux, Prometheus, Grafana, MySQL, Redis, Kafka, Observability, Airflow, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8176684?gh_jid=8176684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CloudFormation, Security, ECS/Fargate, Databricks, Airflow, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7556162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yotpo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8143530?gh_jid=8143530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff Engineer - Office of the CTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8211515?gh_jid=8211515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riskified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel (other)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevEx/DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axonius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Ansible, Docker, CI/CD, Linux, Python, Security, Observability, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7824320003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead (FedRAMP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orcasecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Helm, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://orca.security/about/careers/6149333004?gh_jid=6149333004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4954650101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer- Edge Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saltsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Terraform, Docker, CI/CD, Helm, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://salt.security/job-board?gh_jid=5208152007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-viz-ai-4449757750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform DevOps Engineer - Core Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeen.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-core-platform-at-jeen-ai-4469586881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IVIX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-ivix-4468275010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr. Principal, DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parallel Wireless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4468461559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer (Cortex Agentix Endpoint Security)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-cortex-agentix-endpoint-security-at-palo-alto-networks-4418753719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Checkmarx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-checkmarx-4439196775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4468561146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infinidat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-infinidat-4467985544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer (DevOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akamai Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-akamai-technologies-4461033122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Staff Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-at-palo-alto-networks-4428920772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4468397029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARAN Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aran-software-4470406189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-silverfort-4457951110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead - JB-760</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC | NEXT Technology Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-jb-760-at-pwc-next-technology-solutions-4467986877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethosia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Check Point Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-check-point-software-4467737639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cellebrite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cellebrite-4469980397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assured Allies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-assured-allies-4468548060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZyG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-zyg-4470271839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-jeen-ai-4469586887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4464714816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4464286063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-compie-technologies-4469572961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EasySend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-easysend-4467548799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer III</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CrowdStrike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-iii-at-crowdstrike-4438706386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealth Startup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-stealth-startup-4468441366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bagira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AllCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4470273860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lod, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4468557198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fluent Trade Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-elbit-systems-israel-4394529806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-sela-4468591173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-jobgether-4468712370</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IgniteTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineering - Storage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineering-storage-at-nvidia-4457190574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineering Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conifers.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineering-manager-at-conifers-ai-4467982436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4458308805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-at-calanit-by-one-4470276272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Centrical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-centrical-4468254008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-jobgether-4468496644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-sqlink-group-4468564839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-cyera-4456176236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Center for Educational Technology (CET)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-the-center-for-educational-technology-cet-4467956789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer III, Platform Engineering and Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-iii-platform-engineering-and-infrastructure-at-google-4465561954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Database Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HR Home</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/database-reliability-engineer-at-hr-home-4467191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiverr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fiverr-4458388230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops and Infra Group Tech lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sunbit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-and-infra-group-tech-lead-at-sunbit-4467977092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Millennium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-at-millennium-4457617255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr Staff DevOps Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-staff-devops-platform-engineer-at-palo-alto-networks-4419603015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer - Azure &amp; AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-azure-aws-at-elbit-systems-israel-4458838595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior MLOps Platform Engineer - QuantumBlack, AI by McKinsey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuantumBlack, AI by McKinsey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-mlops-platform-engineer-quantumblack-ai-by-mckinsey-at-quantumblack-ai-by-mckinsey-4423517900</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI SW Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-sw-infrastructure-engineer-at-camtek-4431013854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prisma Photonics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-prisma-photonics-4432235322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure System Engineer</t>
+    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Applied Materials - Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4454115588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4468579109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Talent Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-talent-integration-4466204750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior IT System Administrator 243902</t>
   </si>
   <si>
     <t xml:space="preserve">Experis Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-system-engineer-at-experis-israel-4465531772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Network &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wayve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-infrastructure-engineer-at-wayve-4456949923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4454115588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZutaCore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sderot, South District, Israel</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-it-system-administrator-243902-at-experis-israel-4468981404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mendix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boston, MA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://jobs.lever.co/mendix/f61ca692-a66b-4e9f-a864-ad29e7cd716e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
   </si>
   <si>
     <t xml:space="preserve">Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-infrastructure-engineer-at-zutacore-4456498006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4468579109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talent Integration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-talent-integration-4466204750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mendix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boston, MA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://jobs.lever.co/mendix/f61ca692-a66b-4e9f-a864-ad29e7cd716e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
     <t xml:space="preserve">Helm</t>
   </si>
   <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
     <t xml:space="preserve">Argo CD</t>
   </si>
   <si>
@@ -1242,10 +1242,10 @@
     <t xml:space="preserve">0%</t>
   </si>
   <si>
-    <t xml:space="preserve">44.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.0%</t>
+    <t xml:space="preserve">46.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5%</t>
   </si>
   <si>
     <t xml:space="preserve">Role</t>
@@ -1257,7 +1257,7 @@
     <t xml:space="preserve">Stack</t>
   </si>
   <si>
-    <t xml:space="preserve">Associate Development Operations Engineer</t>
+    <t xml:space="preserve">Development Operations Engineer</t>
   </si>
   <si>
     <t xml:space="preserve">Clarivate</t>
@@ -1272,7 +1272,7 @@
     <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/associate-development-operations-engineer-at-clarivate-4467992253</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
   </si>
   <si>
     <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
@@ -1381,9 +1381,6 @@
   </si>
   <si>
     <t xml:space="preserve">NOC Analyst | Splunk &amp; Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
   </si>
   <si>
     <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Troubleshooting</t>
@@ -1700,7 +1697,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7">
@@ -1708,7 +1705,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
@@ -1716,7 +1713,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
@@ -1724,7 +1721,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="10">
@@ -1796,7 +1793,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20">
@@ -1839,7 +1836,7 @@
         <v>415</v>
       </c>
       <c r="B2" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -1868,7 +1865,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1876,7 +1873,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1895,15 +1892,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B2" s="3">
         <v>19</v>
@@ -1911,7 +1908,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B3" s="3">
         <v>19</v>
@@ -1919,7 +1916,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B4" s="3">
         <v>17</v>
@@ -1927,15 +1924,15 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>374</v>
+        <v>396</v>
       </c>
       <c r="B5" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B6" s="3">
         <v>14</v>
@@ -1943,7 +1940,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B7" s="3">
         <v>13</v>
@@ -1959,7 +1956,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
@@ -1967,7 +1964,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
@@ -1975,7 +1972,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
@@ -1991,7 +1988,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B13" s="3">
         <v>7</v>
@@ -1999,7 +1996,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -2007,7 +2004,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B15" s="3">
         <v>5</v>
@@ -2015,7 +2012,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
@@ -2043,13 +2040,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>511</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>512</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="2">
@@ -2060,10 +2057,10 @@
         <v>30</v>
       </c>
       <c r="C2" s="3">
-        <v>12.9</v>
+        <v>15.5</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2072,28 +2069,28 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C3" s="3">
-        <v>38.3</v>
+        <v>33.7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.1</v>
+        <v>8.3</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E4" s="3"/>
     </row>
@@ -2102,58 +2099,58 @@
         <v>24</v>
       </c>
       <c r="B5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" s="3">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>36.1</v>
+        <v>35.9</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>17.0</v>
+        <v>15.6</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>22.4</v>
+        <v>21.9</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2165,7 +2162,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="2" max="2" width="33" customWidth="1"/>
     <col min="3" max="3" width="47" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -2237,7 +2234,7 @@
         <v>40</v>
       </c>
       <c r="J2" s="3">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -2269,7 +2266,7 @@
         <v>45</v>
       </c>
       <c r="J3" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
@@ -2301,7 +2298,7 @@
         <v>45</v>
       </c>
       <c r="J4" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5">
@@ -2333,7 +2330,7 @@
         <v>52</v>
       </c>
       <c r="J5" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
@@ -2350,7 +2347,7 @@
         <v>36</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>56</v>
@@ -2362,15 +2359,15 @@
         <v>57</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="J6" s="3">
-        <v>42</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>54</v>
@@ -2382,22 +2379,22 @@
         <v>36</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="J7" s="3">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
@@ -2405,10 +2402,10 @@
         <v>62</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>36</v>
@@ -2417,27 +2414,27 @@
         <v>42</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J8" s="3">
-        <v>12</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>36</v>
@@ -2446,30 +2443,28 @@
         <v>36</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>68</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H9" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="J9" s="3">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>36</v>
@@ -2481,27 +2476,27 @@
         <v>42</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H10" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="J10" s="3">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>36</v>
@@ -2513,19 +2508,19 @@
         <v>42</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H11" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="I11" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="J11" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -2533,7 +2528,7 @@
         <v>41</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>36</v>
@@ -2545,27 +2540,27 @@
         <v>42</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H12" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="J12" s="3">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>36</v>
@@ -2577,27 +2572,27 @@
         <v>42</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="I13" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="J13" s="3">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>36</v>
@@ -2609,27 +2604,27 @@
         <v>42</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H14" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>89</v>
-      </c>
       <c r="J14" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>36</v>
@@ -2641,30 +2636,30 @@
         <v>42</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H15" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>93</v>
-      </c>
       <c r="J15" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>36</v>
@@ -2673,30 +2668,30 @@
         <v>42</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H16" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="I16" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="J16" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>36</v>
@@ -2705,30 +2700,30 @@
         <v>42</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H17" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="J17" s="3">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>36</v>
@@ -2737,30 +2732,30 @@
         <v>37</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J18" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>36</v>
@@ -2769,30 +2764,30 @@
         <v>37</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="J19" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>36</v>
@@ -2801,30 +2796,30 @@
         <v>42</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H20" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="J20" s="3">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>115</v>
-      </c>
       <c r="C21" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>36</v>
@@ -2833,30 +2828,30 @@
         <v>42</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J21" s="3">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>119</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>36</v>
@@ -2865,19 +2860,19 @@
         <v>42</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="J22" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
@@ -2885,7 +2880,7 @@
         <v>41</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>36</v>
@@ -2897,27 +2892,27 @@
         <v>42</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="J23" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>36</v>
@@ -2929,27 +2924,27 @@
         <v>37</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H24" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>130</v>
-      </c>
       <c r="J24" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>36</v>
@@ -2961,19 +2956,19 @@
         <v>42</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="I25" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="I25" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="J25" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -2981,42 +2976,42 @@
         <v>34</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>136</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>37</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="J26" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="C27" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>36</v>
@@ -3025,30 +3020,30 @@
         <v>42</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="J27" s="3">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>147</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>36</v>
@@ -3057,59 +3052,59 @@
         <v>42</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>45</v>
       </c>
       <c r="J28" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="C29" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="D29" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="J29" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>156</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>36</v>
@@ -3121,27 +3116,27 @@
         <v>37</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="I30" s="3" t="s">
-        <v>158</v>
-      </c>
       <c r="J30" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B31" s="3" t="s">
         <v>159</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>160</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>36</v>
@@ -3153,19 +3148,19 @@
         <v>37</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="I31" s="3" t="s">
-        <v>163</v>
-      </c>
       <c r="J31" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="32">
@@ -3173,10 +3168,10 @@
         <v>41</v>
       </c>
       <c r="B32" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>164</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>165</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>36</v>
@@ -3189,114 +3184,114 @@
         <v>22</v>
       </c>
       <c r="H32" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>167</v>
-      </c>
       <c r="J32" s="3">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>168</v>
+        <v>41</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>136</v>
+        <v>36</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>172</v>
+        <v>69</v>
       </c>
       <c r="J33" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>41</v>
+        <v>169</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>165</v>
+        <v>49</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="J34" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="J35" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>179</v>
+        <v>41</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>36</v>
@@ -3304,77 +3299,77 @@
       <c r="E36" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F36" s="3" t="s">
-        <v>181</v>
-      </c>
+      <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="J36" s="3">
-        <v>26</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F37" s="3"/>
+        <v>42</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>181</v>
+      </c>
       <c r="G37" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>187</v>
+        <v>88</v>
       </c>
       <c r="J37" s="3">
-        <v>70</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>188</v>
-      </c>
       <c r="C38" s="3" t="s">
-        <v>189</v>
+        <v>49</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>190</v>
+        <v>36</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>192</v>
+        <v>69</v>
       </c>
       <c r="J38" s="3">
         <v>0</v>
@@ -3382,43 +3377,43 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>145</v>
+        <v>169</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>49</v>
+        <v>186</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>36</v>
+        <v>187</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>99</v>
+        <v>189</v>
       </c>
       <c r="J39" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>195</v>
+        <v>144</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>165</v>
+        <v>49</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>36</v>
@@ -3431,84 +3426,84 @@
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>70</v>
+        <v>98</v>
       </c>
       <c r="J40" s="3">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="J41" s="3">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>202</v>
+        <v>112</v>
       </c>
       <c r="J42" s="3">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>36</v>
@@ -3521,117 +3516,117 @@
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J43" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>206</v>
+        <v>180</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>170</v>
+        <v>201</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>136</v>
+        <v>202</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="J44" s="3">
-        <v>0</v>
+        <v>47</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>41</v>
+        <v>169</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>165</v>
+        <v>49</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="J45" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>210</v>
+        <v>169</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>36</v>
+        <v>135</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>99</v>
+        <v>189</v>
       </c>
       <c r="J46" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>213</v>
+        <v>41</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>190</v>
+        <v>36</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>42</v>
@@ -3641,13 +3636,13 @@
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="J47" s="3">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48">
@@ -3655,13 +3650,13 @@
         <v>41</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>190</v>
+        <v>36</v>
       </c>
       <c r="E48" s="3" t="s">
         <v>42</v>
@@ -3671,40 +3666,40 @@
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>219</v>
+        <v>88</v>
       </c>
       <c r="J48" s="3">
-        <v>88</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>183</v>
+        <v>214</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="J49" s="3">
         <v>6</v>
@@ -3712,16 +3707,16 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>41</v>
+        <v>217</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>223</v>
+        <v>186</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>224</v>
+        <v>187</v>
       </c>
       <c r="E50" s="3" t="s">
         <v>42</v>
@@ -3731,40 +3726,40 @@
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>192</v>
+        <v>220</v>
       </c>
       <c r="J50" s="3">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>41</v>
+        <v>221</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>185</v>
+        <v>223</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>192</v>
+        <v>69</v>
       </c>
       <c r="J51" s="3">
         <v>0</v>
@@ -3772,59 +3767,59 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>228</v>
+        <v>41</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>36</v>
+        <v>187</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>192</v>
+        <v>227</v>
       </c>
       <c r="J52" s="3">
-        <v>0</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>231</v>
+        <v>41</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>169</v>
+        <v>228</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>170</v>
+        <v>201</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>136</v>
+        <v>202</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="J53" s="3">
         <v>1</v>
@@ -3832,43 +3827,43 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>183</v>
+        <v>41</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>170</v>
+        <v>209</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>136</v>
+        <v>36</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>235</v>
+        <v>189</v>
       </c>
       <c r="J54" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>237</v>
+        <v>164</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>36</v>
@@ -3881,27 +3876,27 @@
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J55" s="3">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>183</v>
+        <v>235</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>190</v>
+        <v>36</v>
       </c>
       <c r="E56" s="3" t="s">
         <v>37</v>
@@ -3911,57 +3906,57 @@
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>241</v>
+        <v>189</v>
       </c>
       <c r="J56" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>41</v>
+        <v>238</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>242</v>
+        <v>173</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>36</v>
+        <v>135</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>133</v>
+        <v>176</v>
       </c>
       <c r="J57" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>244</v>
+        <v>169</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>36</v>
+        <v>135</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>37</v>
@@ -3971,27 +3966,27 @@
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="J58" s="3">
-        <v>67</v>
+        <v>10</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>248</v>
+        <v>169</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>250</v>
+        <v>223</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>251</v>
+        <v>36</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>37</v>
@@ -4001,57 +3996,57 @@
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="J59" s="3">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>41</v>
+        <v>169</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>136</v>
+        <v>187</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="J60" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>256</v>
+        <v>41</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>258</v>
+        <v>164</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>136</v>
+        <v>36</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>42</v>
@@ -4061,27 +4056,27 @@
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>192</v>
+        <v>132</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>262</v>
+        <v>164</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>136</v>
+        <v>36</v>
       </c>
       <c r="E62" s="3" t="s">
         <v>37</v>
@@ -4091,27 +4086,27 @@
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>52</v>
+        <v>253</v>
       </c>
       <c r="J62" s="3">
-        <v>27</v>
+        <v>68</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>183</v>
+        <v>254</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>37</v>
@@ -4121,57 +4116,57 @@
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>192</v>
+        <v>259</v>
       </c>
       <c r="J63" s="3">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>183</v>
+        <v>41</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>269</v>
+        <v>174</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>192</v>
+        <v>247</v>
       </c>
       <c r="J64" s="3">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>165</v>
+        <v>264</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>36</v>
+        <v>135</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>42</v>
@@ -4181,57 +4176,57 @@
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>45</v>
+        <v>189</v>
       </c>
       <c r="J65" s="3">
-        <v>42</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>277</v>
+        <v>135</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="J66" s="3">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>37</v>
@@ -4241,27 +4236,27 @@
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>133</v>
+        <v>189</v>
       </c>
       <c r="J67" s="3">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>188</v>
+        <v>275</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>237</v>
+        <v>174</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>36</v>
+        <v>135</v>
       </c>
       <c r="E68" s="3" t="s">
         <v>37</v>
@@ -4271,10 +4266,10 @@
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>192</v>
+        <v>69</v>
       </c>
       <c r="J68" s="3">
         <v>0</v>
@@ -4282,29 +4277,29 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>282</v>
+        <v>169</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>172</v>
+        <v>189</v>
       </c>
       <c r="J69" s="3">
         <v>1</v>
@@ -4312,13 +4307,13 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>165</v>
+        <v>223</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>36</v>
@@ -4331,27 +4326,27 @@
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>289</v>
+        <v>69</v>
       </c>
       <c r="J70" s="3">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>42</v>
@@ -4361,117 +4356,117 @@
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>293</v>
+        <v>176</v>
       </c>
       <c r="J71" s="3">
-        <v>65</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>296</v>
+        <v>164</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>136</v>
+        <v>36</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="J72" s="3">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>237</v>
+        <v>285</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>36</v>
+        <v>135</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>78</v>
+        <v>294</v>
       </c>
       <c r="J73" s="3">
-        <v>6</v>
+        <v>66</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>295</v>
+        <v>232</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>296</v>
+        <v>164</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>136</v>
+        <v>36</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="J74" s="3">
-        <v>26</v>
+        <v>34</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>165</v>
+        <v>201</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>36</v>
+        <v>202</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>37</v>
@@ -4481,57 +4476,57 @@
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>306</v>
+        <v>40</v>
       </c>
       <c r="J75" s="3">
-        <v>86</v>
+        <v>21</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>307</v>
+        <v>283</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>192</v>
+        <v>88</v>
       </c>
       <c r="J76" s="3">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>266</v>
+        <v>135</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>37</v>
@@ -4541,57 +4536,57 @@
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>99</v>
+        <v>69</v>
       </c>
       <c r="J77" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>283</v>
+        <v>307</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>284</v>
+        <v>164</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>136</v>
+        <v>36</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>172</v>
+        <v>309</v>
       </c>
       <c r="J78" s="3">
-        <v>1</v>
+        <v>87</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>268</v>
+        <v>311</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>317</v>
+        <v>164</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>251</v>
+        <v>36</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>37</v>
@@ -4601,27 +4596,27 @@
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>192</v>
+        <v>313</v>
       </c>
       <c r="J79" s="3">
-        <v>0</v>
+        <v>59</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>237</v>
+        <v>316</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>36</v>
+        <v>135</v>
       </c>
       <c r="E80" s="3" t="s">
         <v>42</v>
@@ -4631,144 +4626,144 @@
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>85</v>
+        <v>318</v>
       </c>
       <c r="J80" s="3">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>256</v>
+        <v>319</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>165</v>
+        <v>271</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>36</v>
+        <v>272</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J81" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>325</v>
+        <v>300</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>185</v>
+        <v>301</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>36</v>
+        <v>135</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>78</v>
+        <v>324</v>
       </c>
       <c r="J82" s="3">
-        <v>6</v>
+        <v>44</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>328</v>
+        <v>284</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>170</v>
+        <v>285</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>99</v>
+        <v>176</v>
       </c>
       <c r="J83" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>41</v>
+        <v>327</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>330</v>
+        <v>277</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>165</v>
+        <v>328</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>36</v>
+        <v>257</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>89</v>
+        <v>189</v>
       </c>
       <c r="J84" s="3">
-        <v>26</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>36</v>
@@ -4781,30 +4776,30 @@
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="J85" s="3">
-        <v>5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C86" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="D86" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="C86" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="E86" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
@@ -4814,10 +4809,10 @@
         <v>337</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>241</v>
+        <v>88</v>
       </c>
       <c r="J86" s="3">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="87">
@@ -4828,10 +4823,10 @@
         <v>339</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>36</v>
+        <v>135</v>
       </c>
       <c r="E87" s="3" t="s">
         <v>37</v>
@@ -4844,24 +4839,24 @@
         <v>340</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>52</v>
+        <v>98</v>
       </c>
       <c r="J87" s="3">
-        <v>27</v>
+        <v>6</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B88" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="B88" s="3" t="s">
-        <v>295</v>
-      </c>
       <c r="C88" s="3" t="s">
-        <v>296</v>
+        <v>164</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>136</v>
+        <v>36</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>42</v>
@@ -4874,27 +4869,27 @@
         <v>342</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>343</v>
+        <v>88</v>
       </c>
       <c r="J88" s="3">
-        <v>43</v>
+        <v>27</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B89" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="B89" s="3" t="s">
-        <v>180</v>
-      </c>
       <c r="C89" s="3" t="s">
-        <v>223</v>
+        <v>164</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>224</v>
+        <v>36</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
@@ -4904,10 +4899,10 @@
         <v>345</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>343</v>
+        <v>247</v>
       </c>
       <c r="J89" s="3">
-        <v>43</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90">
@@ -4915,134 +4910,132 @@
         <v>346</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>249</v>
+        <v>180</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>250</v>
+        <v>201</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>251</v>
+        <v>202</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F90" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F90" s="3"/>
+      <c r="G90" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H90" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="G90" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H90" s="3" t="s">
-        <v>348</v>
-      </c>
       <c r="I90" s="3" t="s">
-        <v>202</v>
+        <v>324</v>
       </c>
       <c r="J90" s="3">
-        <v>23</v>
+        <v>44</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>41</v>
+        <v>348</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>349</v>
+        <v>222</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>223</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>224</v>
+        <v>36</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>125</v>
+        <v>69</v>
       </c>
       <c r="J91" s="3">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="E92" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F92" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="B92" s="3" t="s">
+      <c r="G92" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H92" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="C92" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E92" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F92" s="3" t="s">
+      <c r="I92" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="G92" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H92" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="I92" s="3" t="s">
-        <v>216</v>
-      </c>
       <c r="J92" s="3">
-        <v>40</v>
+        <v>24</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>355</v>
+        <v>41</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>357</v>
+        <v>201</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>136</v>
+        <v>202</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="J93" s="3">
-        <v>4</v>
+        <v>37</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>213</v>
+        <v>356</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>36</v>
@@ -5050,32 +5043,34 @@
       <c r="E94" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F94" s="3"/>
+      <c r="F94" s="3" t="s">
+        <v>358</v>
+      </c>
       <c r="G94" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>361</v>
+        <v>220</v>
       </c>
       <c r="J94" s="3">
-        <v>77</v>
+        <v>41</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C95" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="B95" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="D95" s="3" t="s">
-        <v>36</v>
+        <v>135</v>
       </c>
       <c r="E95" s="3" t="s">
         <v>37</v>
@@ -5085,21 +5080,21 @@
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>78</v>
+        <v>132</v>
       </c>
       <c r="J95" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="B96" s="3" t="s">
         <v>365</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>366</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>49</v>
@@ -5115,27 +5110,27 @@
         <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>52</v>
       </c>
       <c r="J96" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>369</v>
+        <v>232</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>262</v>
+        <v>164</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>136</v>
+        <v>36</v>
       </c>
       <c r="E97" s="3" t="s">
         <v>37</v>
@@ -5145,56 +5140,54 @@
         <v>22</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>130</v>
+        <v>369</v>
       </c>
       <c r="J97" s="3">
-        <v>32</v>
+        <v>13</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B98" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="B98" s="3" t="s">
-        <v>372</v>
-      </c>
       <c r="C98" s="3" t="s">
-        <v>373</v>
+        <v>268</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E98" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F98" s="3" t="s">
-        <v>374</v>
-      </c>
+      <c r="F98" s="3"/>
       <c r="G98" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>78</v>
+        <v>129</v>
       </c>
       <c r="J98" s="3">
-        <v>6</v>
+        <v>33</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>237</v>
+        <v>223</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>36</v>
@@ -5207,24 +5200,24 @@
         <v>22</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="J99" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>36</v>
@@ -5237,47 +5230,77 @@
         <v>22</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J100" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>384</v>
+        <v>209</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>136</v>
+        <v>36</v>
       </c>
       <c r="E101" s="3" t="s">
         <v>42</v>
       </c>
       <c r="F101" s="3"/>
       <c r="G101" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>192</v>
+        <v>69</v>
       </c>
       <c r="J101" s="3">
         <v>0</v>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F102" s="3"/>
+      <c r="G102" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="J102" s="3">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J101"/>
+  <autoFilter ref="A1:J102"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5379,6 +5402,7 @@
     <hyperlink ref="H99" r:id="rId98"/>
     <hyperlink ref="H100" r:id="rId99"/>
     <hyperlink ref="H101" r:id="rId100"/>
+    <hyperlink ref="H102" r:id="rId101"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5386,9 +5410,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="1" max="1" width="40" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
@@ -5420,32 +5444,32 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>183</v>
+        <v>67</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>188</v>
+        <v>63</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>189</v>
+        <v>36</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>191</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>183</v>
+        <v>41</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>206</v>
+        <v>167</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5453,18 +5477,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>207</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>41</v>
+        <v>169</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>222</v>
+        <v>170</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>223</v>
+        <v>49</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5472,7 +5496,7 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>225</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5">
@@ -5480,10 +5504,10 @@
         <v>41</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>226</v>
+        <v>183</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>185</v>
+        <v>49</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5491,18 +5515,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>227</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>228</v>
+        <v>169</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>165</v>
+        <v>49</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5510,18 +5534,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>230</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>256</v>
+        <v>221</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>257</v>
+        <v>222</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>258</v>
+        <v>223</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5529,18 +5553,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>259</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>183</v>
+        <v>274</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>265</v>
+        <v>174</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5548,18 +5572,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>183</v>
+        <v>280</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>269</v>
+        <v>223</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5567,18 +5591,18 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>280</v>
+        <v>303</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>188</v>
+        <v>304</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>237</v>
+        <v>285</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5586,18 +5610,18 @@
         <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>281</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>307</v>
+        <v>348</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>308</v>
+        <v>222</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>309</v>
+        <v>223</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5605,18 +5629,18 @@
         <v>22</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>310</v>
+        <v>349</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>316</v>
+        <v>379</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>268</v>
+        <v>380</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>317</v>
+        <v>209</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -5624,49 +5648,11 @@
         <v>22</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G14"/>
+  <autoFilter ref="A1:G12"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5679,8 +5665,6 @@
     <hyperlink ref="G10" r:id="rId9"/>
     <hyperlink ref="G11" r:id="rId10"/>
     <hyperlink ref="G12" r:id="rId11"/>
-    <hyperlink ref="G13" r:id="rId12"/>
-    <hyperlink ref="G14" r:id="rId13"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5694,18 +5678,18 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>386</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B2" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -5713,55 +5697,55 @@
         <v>181</v>
       </c>
       <c r="B3" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B5" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B7" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B8" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="B9" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -5774,7 +5758,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
@@ -5785,7 +5769,7 @@
         <v>395</v>
       </c>
       <c r="B12" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
@@ -5801,7 +5785,7 @@
         <v>397</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -5809,7 +5793,7 @@
         <v>398</v>
       </c>
       <c r="B15" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -5827,7 +5811,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="1" max="1" width="27" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5841,15 +5825,15 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B2" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B3" s="3">
         <v>5</v>
@@ -5865,7 +5849,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5873,7 +5857,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>115</v>
+        <v>180</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5881,7 +5865,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>180</v>
+        <v>232</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5889,23 +5873,23 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>249</v>
+        <v>54</v>
       </c>
       <c r="B8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>295</v>
+        <v>126</v>
       </c>
       <c r="B9" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>127</v>
+        <v>173</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5913,7 +5897,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>169</v>
+        <v>222</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5921,7 +5905,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>188</v>
+        <v>255</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5929,7 +5913,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5937,7 +5921,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5945,15 +5929,15 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>48</v>
+        <v>300</v>
       </c>
       <c r="B15" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>134</v>
+        <v>48</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -5967,7 +5951,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
@@ -5991,13 +5975,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C2" s="3">
-        <v>26.9</v>
+        <v>35.8</v>
       </c>
       <c r="D2" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -6005,7 +5989,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C3" s="3">
         <v>23.8</v>
@@ -6033,7 +6017,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="C5" s="3">
         <v>10.1</v>
@@ -6047,13 +6031,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>115</v>
+        <v>54</v>
       </c>
       <c r="C6" s="3">
-        <v>10.1</v>
+        <v>5.0</v>
       </c>
       <c r="D6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -6061,10 +6045,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>249</v>
+        <v>180</v>
       </c>
       <c r="C7" s="3">
-        <v>4.3</v>
+        <v>4.0</v>
       </c>
       <c r="D7" s="3">
         <v>3</v>
@@ -6075,13 +6059,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>180</v>
+        <v>126</v>
       </c>
       <c r="C8" s="3">
-        <v>4.0</v>
+        <v>3.6</v>
       </c>
       <c r="D8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6089,13 +6073,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>127</v>
+        <v>232</v>
       </c>
       <c r="C9" s="3">
         <v>3.6</v>
       </c>
       <c r="D9" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -6103,13 +6087,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>295</v>
+        <v>48</v>
       </c>
       <c r="C10" s="3">
-        <v>3.6</v>
+        <v>3.0</v>
       </c>
       <c r="D10" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -6117,13 +6101,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>48</v>
+        <v>255</v>
       </c>
       <c r="C11" s="3">
-        <v>3.0</v>
+        <v>2.9</v>
       </c>
       <c r="D11" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -6131,7 +6115,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C12" s="3">
         <v>2.6</v>
@@ -6145,7 +6129,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C13" s="3">
         <v>2.4</v>
@@ -6159,7 +6143,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C14" s="3">
         <v>2.4</v>
@@ -6173,7 +6157,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>188</v>
+        <v>222</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -6187,7 +6171,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -6235,7 +6219,7 @@
         <v>37</v>
       </c>
       <c r="B3" s="3">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>407</v>
@@ -6246,7 +6230,7 @@
         <v>42</v>
       </c>
       <c r="B4" s="3">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>408</v>
@@ -6276,28 +6260,28 @@
         <v>36</v>
       </c>
       <c r="B2" s="3">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B3" s="3">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>251</v>
+        <v>187</v>
       </c>
       <c r="B5" s="3">
         <v>4</v>
@@ -6305,7 +6289,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>224</v>
+        <v>257</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -6313,7 +6297,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="B7" s="3">
         <v>2</v>
@@ -6321,7 +6305,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>277</v>
+        <v>336</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -6407,7 +6391,7 @@
         <v>417</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3">
@@ -6421,7 +6405,7 @@
         <v>419</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>420</v>
@@ -6439,7 +6423,7 @@
         <v>422</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4">
@@ -6453,7 +6437,7 @@
         <v>424</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>425</v>
@@ -6485,7 +6469,7 @@
         <v>430</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>415</v>
@@ -6503,7 +6487,7 @@
         <v>432</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6">
@@ -6517,7 +6501,7 @@
         <v>434</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>415</v>
@@ -6549,7 +6533,7 @@
         <v>439</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>420</v>
@@ -6567,7 +6551,7 @@
         <v>441</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8">
@@ -6613,7 +6597,7 @@
         <v>449</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>450</v>
@@ -6631,7 +6615,7 @@
         <v>452</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10">
@@ -6642,10 +6626,10 @@
         <v>453</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>454</v>
+        <v>275</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>415</v>
@@ -6654,16 +6638,16 @@
         <v>60</v>
       </c>
       <c r="G10" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>456</v>
-      </c>
       <c r="J10" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="11">
@@ -6671,13 +6655,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>458</v>
-      </c>
       <c r="D11" s="3" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>450</v>
@@ -6686,16 +6670,16 @@
         <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>460</v>
-      </c>
       <c r="J11" s="3" t="s">
-        <v>202</v>
+        <v>353</v>
       </c>
     </row>
     <row r="12">
@@ -6703,13 +6687,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>462</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>463</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>450</v>
@@ -6718,16 +6702,16 @@
         <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>465</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13">
@@ -6735,28 +6719,28 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>467</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>468</v>
       </c>
       <c r="F13" s="3">
         <v>46</v>
       </c>
       <c r="G13" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>469</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>470</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>52</v>
@@ -6767,13 +6751,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>415</v>
@@ -6782,16 +6766,16 @@
         <v>44</v>
       </c>
       <c r="G14" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>473</v>
-      </c>
       <c r="J14" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15">
@@ -6799,13 +6783,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>475</v>
-      </c>
       <c r="D15" s="3" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>420</v>
@@ -6814,16 +6798,16 @@
         <v>39</v>
       </c>
       <c r="G15" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>477</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16">
@@ -6831,13 +6815,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>479</v>
-      </c>
       <c r="D16" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>415</v>
@@ -6846,16 +6830,16 @@
         <v>36</v>
       </c>
       <c r="G16" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>481</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="17">
@@ -6863,13 +6847,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>484</v>
-      </c>
       <c r="D17" s="3" t="s">
-        <v>276</v>
+        <v>335</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>415</v>
@@ -6878,16 +6862,16 @@
         <v>32</v>
       </c>
       <c r="G17" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>486</v>
-      </c>
       <c r="J17" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="18">
@@ -6895,13 +6879,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>415</v>
@@ -6910,16 +6894,16 @@
         <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>489</v>
-      </c>
       <c r="J18" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19">
@@ -6927,13 +6911,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>450</v>
@@ -6942,16 +6926,16 @@
         <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>492</v>
-      </c>
       <c r="J19" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="20">
@@ -6959,13 +6943,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>494</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>495</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>450</v>
@@ -6974,16 +6958,16 @@
         <v>27</v>
       </c>
       <c r="G20" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>497</v>
-      </c>
       <c r="J20" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21">
@@ -6991,10 +6975,10 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>498</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>499</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>49</v>
@@ -7006,13 +6990,13 @@
         <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>500</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>501</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>40</v>

--- a/reports/devops-jobs-israel-2026-W39.xlsx
+++ b/reports/devops-jobs-israel-2026-W39.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="496">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23T11:23:07</t>
+    <t xml:space="preserve">2026-09-24T11:35:11</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -93,1477 +93,1411 @@
     <t xml:space="preserve">greenhouse</t>
   </si>
   <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bucket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seniority</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skills</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First Seen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevSecOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, CloudFormation, Security, Container Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8574774002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Helm, Pulumi, CloudFormation, Networking, Security, Argo CD, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8356511002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8171972002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoneer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Python, Bash/Shell, Helm, Prometheus, Grafana, Networking, Security, Argo CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.payoneer.com/careers/position/8132080/?gh_jid=8132080</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Architect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jfrog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, Python, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=8188177&amp;gh_jid=8188177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Advocate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Developer Experience (DevEx) Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Python, Security, Observability, Backstage/IDP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4693375006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cloud Security Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668069006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Cyber Defense Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4677810006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4700779006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevSecOps Manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4704221006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Director of Platform Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior SRE Engineer /Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Terraform, Ansible, Docker, CI/CD, Linux, Python, Prometheus, Grafana, ELK/Elastic, Networking, Argo CD, Rust, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8070135?gh_jid=8070135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer, Traffic Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Linux, Istio, Service Mesh, Nginx, Networking, Observability, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8200807?gh_jid=8200807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Developer – Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Docker, Linux, Prometheus, Grafana, MySQL, Redis, Kafka, Observability, Airflow, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8176684?gh_jid=8176684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Similarweb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Data Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CloudFormation, Security, ECS/Fargate, Databricks, Airflow, Spark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7556162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director of Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yotpo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Observability</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8143530?gh_jid=8143530</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff Engineer - Office of the CTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8211515?gh_jid=8211515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Riskified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lisbon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel (other)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevEx/DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Axonius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Ansible, Docker, CI/CD, Linux, Python, Security, Observability, FinOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7824320003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transmitsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Lead (FedRAMP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orcasecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Helm, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://orca.security/about/careers/6149333004?gh_jid=6149333004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Optimove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4954650101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform Engineer- Edge Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saltsecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, Terraform, Docker, CI/CD, Helm, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://salt.security/job-board?gh_jid=5208152007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Viz.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-viz-ai-4449757750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-radware-4468903264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-at-palo-alto-networks-4469323268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CommBox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commbox-4470453217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform DevOps Engineer - Core Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeen.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-core-platform-at-jeen-ai-4469586881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4469727405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nayax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nayax-4469432294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4451477598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer (DevOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akamai Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-akamai-technologies-4461033122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pagaya-4316888825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Secrets Manager)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-secrets-manager-at-palo-alto-networks-4419602029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4469714710</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireArc Technologies .LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-firearc-technologies-ltd-4470443498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARAN Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aran-software-4470406189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akeyless Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4457183616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ethosia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer 4218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank Hapoalim בנק הפועלים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-4218-at-bank-hapoalim-%D7%91%D7%A0%D7%A7-%D7%94%D7%A4%D7%95%D7%A2%D7%9C%D7%99%D7%9D-4469435452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cellebrite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cellebrite-4469980397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assured Allies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-assured-allies-4468548060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZyG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-zyg-4470271839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-jeen-ai-4469586887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nanox Vision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nanox-vision-4470995085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4451663128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4464714816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4464286063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EasySend</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-easysend-4467548799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CrowdStrike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-iii-at-crowdstrike-4438706386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth Startup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-stealth-startup-4468441366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AllCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4470273860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-confidential-careers-4468585946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lod, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4468557198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer 4210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-4210-at-bank-hapoalim-%D7%91%D7%A0%D7%A7-%D7%94%D7%A4%D7%95%D7%A2%D7%9C%D7%99%D7%9D-4469434426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stealth Company</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-company-4468995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-wix-4464485443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-jobgether-4468712370</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IgniteTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VP, Site Reliability Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/vp-site-reliability-engineering-at-oracle-4459580128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4458308805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Director, Site Reliability Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DuckDuckGo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-site-reliability-engineering-at-duckduckgo-4469057695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Production Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhino Federated Computing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manager, Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crusoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-production-engineering-at-crusoe-4442593613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARMAN International</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-jobgether-4468496644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Data Infrastructure Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-team-leader-at-evoke-4470918616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Database Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sharpies PRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/database-reliability-engineer-at-sharpies-pro-4469456732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-sqlink-group-4468564839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fiverr-4458388230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sr Staff DevOps Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-staff-devops-platform-engineer-at-palo-alto-networks-4419603015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraCyte Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-teracyte-analytics-4469729261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer - Azure &amp; AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-azure-aws-at-elbit-systems-israel-4458838595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraSky</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior MLOps Platform Engineer - QuantumBlack, AI by McKinsey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuantumBlack, AI by McKinsey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-mlops-platform-engineer-quantumblack-ai-by-mckinsey-at-quantumblack-ai-by-mckinsey-4423517900</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semperis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-security-engineer-at-semperis-4438770193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4468579109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior IT System Administrator 243902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-it-system-administrator-243902-at-experis-israel-4468981404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Deployment Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-deployment-engineer-at-jeen-ai-4471412751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAF/CDN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strength Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Learning Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Development Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clarivate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SysAdmin / NOC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon Web Services (AWS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Analyst | Splunk &amp; Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-splunk-infrastructure-at-confidential-careers-4465957826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Specialist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TytoCare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator 7992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sysnet part of Amanet Tec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Cloud (any), Virtualization, Active Directory, Windows Server, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-7992-at-sysnet-part-of-amanet-tec-4467053868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior SysAdmin / Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elapsed (s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">indeed_il</t>
+  </si>
+  <si>
     <t xml:space="preserve">lever</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bucket</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Seniority</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skills</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First Seen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevSecOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Terraform, Docker, CI/CD, CloudFormation, Security, Container Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8574774002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Helm, Pulumi, CloudFormation, Networking, Security, Argo CD, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8356511002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8171972002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Payoneer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Python, Bash/Shell, Helm, Prometheus, Grafana, Networking, Security, Argo CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.payoneer.com/careers/position/8132080/?gh_jid=8132080</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Architect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jfrog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, Python, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=8188177&amp;gh_jid=8188177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Advocate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Developer Experience (DevEx) Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Python, Security, Observability, Backstage/IDP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4693375006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of Quality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4695788006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cloud Security Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4668069006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Cyber Defense Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4677810006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CI/CD, Linux, Python, Bash/Shell, Helm, Prometheus, Grafana, Datadog, Security, Argo CD, Observability, Crossplane, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4700779006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevSecOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, CI/CD, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4704221006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Director of Platform Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, Docker, CI/CD, Security, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4672099006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior SRE Engineer /Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, CI/CD, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4673075006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Platform Engineering Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Linux, Kafka, Airflow, dbt, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903597?gh_jid=7903597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Terraform, Ansible, Docker, CI/CD, Linux, Python, Prometheus, Grafana, ELK/Elastic, Networking, Argo CD, Rust, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8070135?gh_jid=8070135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer, Traffic Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Linux, Istio, Service Mesh, Nginx, Networking, Observability, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8200807?gh_jid=8200807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Developer – Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Docker, Linux, Prometheus, Grafana, MySQL, Redis, Kafka, Observability, Airflow, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8176684?gh_jid=8176684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Development Team Leader – Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/7903594?gh_jid=7903594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Backend Engineer, Platform Foundations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similarweb</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Ansible, Docker, CI/CD, Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7962665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Data Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, Docker, CloudFormation, Security, ECS/Fargate, Databricks, Airflow, Spark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7556162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, GCP, Docker, Linux, Python, Networking, Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/similarweb/jobs/7938197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director of Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yotpo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Observability</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8143530?gh_jid=8143530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff Engineer - Office of the CTO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.yotpo.com/careers/gid-8211515?gh_jid=8211515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Riskified</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lisbon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel (other)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Terraform, Linux, Python, Go, Networking, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.riskified.com/careers/job-description/?gh_jid=8587299002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevEx/DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Axonius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, Terraform, Ansible, Docker, CI/CD, Linux, Python, Security, Observability, FinOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.axonius.com/company/careers/open-jobs?gh_jid=7824320003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transmitsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Gush Dan, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, GCP, CI/CD, Helm, Grafana, Security, Argo CD, AI/MLOps, WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead (FedRAMP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orcasecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Helm, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://orca.security/about/careers/6149333004?gh_jid=6149333004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Optimove</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.eu.greenhouse.io/optimove/jobs/4954650101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform Engineer- Edge Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saltsecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, Terraform, Docker, CI/CD, Helm, Security, Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://salt.security/job-board?gh_jid=5208152007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viz.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-viz-ai-4449757750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radware</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-radware-4468903264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CommBox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commbox-4470453217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform DevOps Engineer - Core Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeen.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-core-platform-at-jeen-ai-4469586881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IVIX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-ivix-4468275010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal DevOps Engineer (Cortex Agentix Endpoint Security)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-cortex-agentix-endpoint-security-at-palo-alto-networks-4418753719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nayax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nayax-4469432294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4468561146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infinidat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-infinidat-4467985544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer (DevOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akamai Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-akamai-technologies-4461033122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer - Cloud Infra Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-cloud-infra-team-at-wix-4468397029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Secrets Manager)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-secrets-manager-at-palo-alto-networks-4419602029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireArc Technologies .LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-firearc-technologies-ltd-4470443498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARAN Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aran-software-4470406189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akeyless Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4457183616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-silverfort-4457951110</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead - JB-760</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PwC | NEXT Technology Solutions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-jb-760-at-pwc-next-technology-solutions-4467986877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethosia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer 4218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bank Hapoalim בנק הפועלים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-4218-at-bank-hapoalim-%D7%91%D7%A0%D7%A7-%D7%94%D7%A4%D7%95%D7%A2%D7%9C%D7%99%D7%9D-4469435452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fetcherr-4429844723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cellebrite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cellebrite-4469980397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assured Allies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-assured-allies-4468548060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZyG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-zyg-4470271839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-jeen-ai-4469586887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4464714816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4464286063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compie Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-compie-technologies-4469572961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EasySend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-easysend-4467548799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer III</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CrowdStrike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-iii-at-crowdstrike-4438706386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealth Startup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-stealth-startup-4468441366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bagira</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Modiin-Maccabim-Reut, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-lead-at-bagira-4368663100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rehovot, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-devops-engineer-at-thales-4343562293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AllCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4470273860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-confidential-careers-4468585946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lod, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4468557198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yael Korentec Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-manager-at-yael-korentec-technologies-4470914031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-jobgether-4468712370</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IgniteTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VP, Site Reliability Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/vp-site-reliability-engineering-at-oracle-4459580128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4458308805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director, Site Reliability Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DuckDuckGo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-site-reliability-engineering-at-duckduckgo-4469057695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manager, Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crusoe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-production-engineering-at-crusoe-4442593613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HARMAN International</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Centrical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-centrical-4468254008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-jobgether-4468496644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-sqlink-group-4468564839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyera</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-team-lead-at-cyera-4456176236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Head of DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fluent Trade Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-at-fluent-trade-technologies-4372997510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Database Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HR Home</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/database-reliability-engineer-at-hr-home-4467191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiverr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fiverr-4458388230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr Staff DevOps Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-staff-devops-platform-engineer-at-palo-alto-networks-4419603015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer 4210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-4210-at-bank-hapoalim-%D7%91%D7%A0%D7%A7-%D7%94%D7%A4%D7%95%D7%A2%D7%9C%D7%99%D7%9D-4469434426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer - Azure &amp; AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-azure-aws-at-elbit-systems-israel-4458838595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior MLOps Platform Engineer - QuantumBlack, AI by McKinsey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuantumBlack, AI by McKinsey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-mlops-platform-engineer-quantumblack-ai-by-mckinsey-at-quantumblack-ai-by-mckinsey-4423517900</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI SW Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Camtek</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Migdal HaEmek, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-sw-infrastructure-engineer-at-camtek-4431013854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Network &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wayve</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-network-infrastructure-engineer-at-wayve-4456949923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computing Infrastructure Engineer – SW GPS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Applied Materials - Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/computing-infrastructure-engineer-%E2%80%93-sw-gps-at-applied-materials-israel-4454115588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4468579109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Talent Integration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-talent-integration-4466204750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior IT System Administrator 243902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-it-system-administrator-243902-at-experis-israel-4468981404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mendix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boston, MA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://jobs.lever.co/mendix/f61ca692-a66b-4e9f-a864-ad29e7cd716e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WAF/CDN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Roles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rank</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strength Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Role</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Learning Score</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Development Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clarivate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SysAdmin / NOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, CI/CD, Terraform/IaC, Networking, Monitoring, Virtualization, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/development-operations-engineer-at-clarivate-4467992253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon Web Services (AWS)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-web-services-aws-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Analyst | Splunk &amp; Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-splunk-infrastructure-at-confidential-careers-4465957826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Specialist</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Networking, Monitoring, Databases, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-specialist-at-upwind-security-4460871956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lumana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Caesarea, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-lumana-4463708633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TytoCare</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator 7992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sysnet part of Amanet Tec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Virtualization, Active Directory, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-7992-at-sysnet-part-of-amanet-tec-4467053868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Field Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mornex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior SysAdmin / Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elapsed (s)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">indeed_il</t>
   </si>
   <si>
     <t xml:space="preserve">alljobs</t>
@@ -1697,7 +1631,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7">
@@ -1705,7 +1639,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -1713,7 +1647,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9">
@@ -1793,7 +1727,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20">
@@ -1801,15 +1735,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="3">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1825,23 +1751,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>403</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>415</v>
+        <v>394</v>
       </c>
       <c r="B2" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="B3" s="3">
         <v>7</v>
@@ -1849,15 +1775,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>450</v>
+        <v>429</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>425</v>
+        <v>399</v>
       </c>
       <c r="B5" s="3">
         <v>1</v>
@@ -1865,7 +1791,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>467</v>
+        <v>446</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1873,7 +1799,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>501</v>
+        <v>479</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1886,69 +1812,69 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>385</v>
+        <v>364</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>502</v>
+        <v>480</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>503</v>
+        <v>481</v>
       </c>
       <c r="B2" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>504</v>
+        <v>482</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>505</v>
+        <v>483</v>
       </c>
       <c r="B4" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>396</v>
+        <v>373</v>
       </c>
       <c r="B5" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>394</v>
+        <v>375</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>506</v>
+        <v>484</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>395</v>
+        <v>374</v>
       </c>
       <c r="B8" s="3">
         <v>11</v>
@@ -1956,7 +1882,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>507</v>
+        <v>485</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
@@ -1964,7 +1890,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>388</v>
+        <v>367</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
@@ -1972,7 +1898,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>389</v>
+        <v>368</v>
       </c>
       <c r="B11" s="3">
         <v>8</v>
@@ -1980,7 +1906,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>393</v>
+        <v>372</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -1988,7 +1914,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="B13" s="3">
         <v>7</v>
@@ -1996,7 +1922,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>390</v>
+        <v>369</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -2004,18 +1930,18 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>508</v>
+        <v>370</v>
       </c>
       <c r="B15" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>509</v>
+        <v>486</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2040,13 +1966,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>510</v>
+        <v>487</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>511</v>
+        <v>488</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>512</v>
+        <v>489</v>
       </c>
     </row>
     <row r="2">
@@ -2054,13 +1980,13 @@
         <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2" s="3">
-        <v>15.5</v>
+        <v>12.9</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>513</v>
+        <v>490</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -2069,88 +1995,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C3" s="3">
-        <v>33.7</v>
+        <v>39.1</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>513</v>
+        <v>490</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>514</v>
+        <v>491</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.3</v>
+        <v>9.8</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>513</v>
+        <v>490</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>24</v>
+        <v>492</v>
       </c>
       <c r="B5" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>513</v>
+        <v>490</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>515</v>
+        <v>493</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>35.9</v>
+        <v>32.9</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>513</v>
+        <v>490</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>516</v>
+        <v>494</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>513</v>
+        <v>490</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>517</v>
+        <v>495</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>21.9</v>
+        <v>21.1</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>513</v>
+        <v>490</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2162,8 +2088,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
-    <col min="2" max="2" width="33" customWidth="1"/>
-    <col min="3" max="3" width="47" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2175,277 +2101,279 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="C2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="J2" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="J3" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>42</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J4" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="J5" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>56</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="I6" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="J6" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J7" s="3">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>63</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>64</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H8" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="J8" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F9" s="3"/>
       <c r="G9" s="3" t="s">
         <v>23</v>
       </c>
@@ -2456,7 +2384,7 @@
         <v>69</v>
       </c>
       <c r="J9" s="3">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10">
@@ -2464,16 +2392,16 @@
         <v>70</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>71</v>
@@ -2488,56 +2416,56 @@
         <v>73</v>
       </c>
       <c r="J10" s="3">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>75</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H11" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="I11" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="J11" s="3">
-        <v>7</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>78</v>
@@ -2552,7 +2480,7 @@
         <v>80</v>
       </c>
       <c r="J12" s="3">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -2560,16 +2488,16 @@
         <v>81</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>82</v>
@@ -2584,7 +2512,7 @@
         <v>84</v>
       </c>
       <c r="J13" s="3">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
@@ -2592,16 +2520,16 @@
         <v>85</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>86</v>
@@ -2616,7 +2544,7 @@
         <v>88</v>
       </c>
       <c r="J14" s="3">
-        <v>27</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -2624,48 +2552,48 @@
         <v>89</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>63</v>
+        <v>90</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="J15" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>96</v>
@@ -2680,7 +2608,7 @@
         <v>98</v>
       </c>
       <c r="J16" s="3">
-        <v>6</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17">
@@ -2688,16 +2616,16 @@
         <v>99</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D17" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>100</v>
@@ -2709,39 +2637,39 @@
         <v>101</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="J17" s="3">
-        <v>58</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
       <c r="J18" s="3">
         <v>9</v>
@@ -2749,34 +2677,34 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H19" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="I19" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="J19" s="3">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -2784,31 +2712,31 @@
         <v>109</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="J20" s="3">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21">
@@ -2816,16 +2744,16 @@
         <v>113</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="D21" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>115</v>
@@ -2837,266 +2765,266 @@
         <v>116</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="J21" s="3">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>117</v>
+        <v>40</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>119</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>121</v>
-      </c>
       <c r="J22" s="3">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>41</v>
+        <v>121</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="F23" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J23" s="3">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>127</v>
+        <v>59</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H24" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="I24" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="J24" s="3">
-        <v>33</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="F25" s="3" t="s">
-        <v>60</v>
+        <v>132</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="J25" s="3">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>34</v>
+        <v>135</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>134</v>
+        <v>91</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>135</v>
+        <v>35</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J26" s="3">
-        <v>12</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>95</v>
+        <v>142</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>143</v>
+        <v>44</v>
       </c>
       <c r="J27" s="3">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>36</v>
+        <v>131</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="J28" s="3">
-        <v>43</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>151</v>
+        <v>35</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>135</v>
+        <v>35</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>152</v>
+        <v>123</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="I29" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="J29" s="3">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30">
@@ -3107,51 +3035,49 @@
         <v>155</v>
       </c>
       <c r="C30" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E30" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D30" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>37</v>
-      </c>
       <c r="F30" s="3" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J30" s="3">
-        <v>35</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>158</v>
+        <v>40</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>159</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>36</v>
+        <v>160</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>160</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>161</v>
@@ -3160,54 +3086,54 @@
         <v>162</v>
       </c>
       <c r="J31" s="3">
-        <v>16</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>163</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H32" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="J32" s="3">
-        <v>47</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>41</v>
+        <v>166</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>167</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
@@ -3217,7 +3143,7 @@
         <v>168</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>69</v>
+        <v>169</v>
       </c>
       <c r="J33" s="3">
         <v>0</v>
@@ -3225,141 +3151,139 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D34" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>69</v>
+        <v>165</v>
       </c>
       <c r="J34" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J35" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>98</v>
+        <v>169</v>
       </c>
       <c r="J36" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>179</v>
+        <v>40</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>180</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>164</v>
+        <v>48</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F37" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H37" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="G37" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="I37" s="3" t="s">
-        <v>88</v>
+        <v>165</v>
       </c>
       <c r="J37" s="3">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
@@ -3369,117 +3293,117 @@
         <v>184</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="J38" s="3">
-        <v>0</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>187</v>
+        <v>35</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>189</v>
+        <v>65</v>
       </c>
       <c r="J39" s="3">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>49</v>
+        <v>160</v>
       </c>
       <c r="D40" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E40" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="J40" s="3">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D41" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E41" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="J41" s="3">
-        <v>23</v>
+        <v>73</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="B42" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>36</v>
-      </c>
       <c r="E42" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
@@ -3489,27 +3413,27 @@
         <v>196</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>112</v>
+        <v>162</v>
       </c>
       <c r="J42" s="3">
-        <v>26</v>
+        <v>48</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="D43" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E43" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
@@ -3519,87 +3443,87 @@
         <v>199</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>98</v>
+        <v>169</v>
       </c>
       <c r="J43" s="3">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>180</v>
-      </c>
       <c r="C44" s="3" t="s">
-        <v>201</v>
+        <v>48</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>202</v>
+        <v>35</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="J44" s="3">
-        <v>47</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>49</v>
+        <v>175</v>
       </c>
       <c r="D45" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E45" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>69</v>
+        <v>204</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>169</v>
+        <v>40</v>
       </c>
       <c r="B46" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="D46" s="3" t="s">
-        <v>135</v>
+        <v>35</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
@@ -3609,207 +3533,207 @@
         <v>207</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="J46" s="3">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="J47" s="3">
-        <v>29</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>41</v>
+        <v>215</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="D48" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>88</v>
+        <v>165</v>
       </c>
       <c r="J48" s="3">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>214</v>
+        <v>40</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>36</v>
+        <v>195</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>98</v>
+        <v>204</v>
       </c>
       <c r="J49" s="3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>217</v>
+        <v>40</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>187</v>
+        <v>35</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>220</v>
+        <v>204</v>
       </c>
       <c r="J50" s="3">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>221</v>
+        <v>170</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>222</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>223</v>
+        <v>160</v>
       </c>
       <c r="D51" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="I51" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="I51" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="J51" s="3">
-        <v>0</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>41</v>
+        <v>225</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>187</v>
+        <v>35</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="J52" s="3">
-        <v>89</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>41</v>
+        <v>228</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>228</v>
+        <v>174</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>202</v>
+        <v>131</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
@@ -3819,87 +3743,87 @@
         <v>229</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="J53" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>41</v>
+        <v>230</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>209</v>
+        <v>160</v>
       </c>
       <c r="D54" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E54" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>189</v>
+        <v>233</v>
       </c>
       <c r="J54" s="3">
-        <v>1</v>
+        <v>64</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="D55" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E55" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>234</v>
+        <v>169</v>
       </c>
       <c r="J55" s="3">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>235</v>
+        <v>170</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>236</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D56" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E56" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
@@ -3909,327 +3833,327 @@
         <v>237</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>189</v>
+        <v>238</v>
       </c>
       <c r="J56" s="3">
-        <v>1</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>238</v>
+        <v>170</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>173</v>
+        <v>239</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>176</v>
+        <v>241</v>
       </c>
       <c r="J57" s="3">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>135</v>
+        <v>35</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F58" s="3"/>
       <c r="G58" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="I58" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>242</v>
-      </c>
       <c r="J58" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>169</v>
+        <v>40</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>223</v>
+        <v>160</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>242</v>
+        <v>128</v>
       </c>
       <c r="J59" s="3">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>169</v>
+        <v>246</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>187</v>
+        <v>35</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J60" s="3">
-        <v>3</v>
+        <v>69</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>41</v>
+        <v>250</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>164</v>
+        <v>252</v>
       </c>
       <c r="D61" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E61" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="F61" s="3"/>
       <c r="G61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>132</v>
+        <v>255</v>
       </c>
       <c r="J61" s="3">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>250</v>
+        <v>40</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>36</v>
+        <v>131</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="J62" s="3">
-        <v>68</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>254</v>
+        <v>170</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>259</v>
+        <v>204</v>
       </c>
       <c r="J63" s="3">
-        <v>20</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>41</v>
+        <v>263</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F64" s="3"/>
       <c r="G64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>247</v>
+        <v>165</v>
       </c>
       <c r="J64" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>262</v>
+        <v>170</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F65" s="3"/>
       <c r="G65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="J65" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>267</v>
+        <v>216</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>268</v>
+        <v>183</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>135</v>
+        <v>35</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>52</v>
+        <v>165</v>
       </c>
       <c r="J66" s="3">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>169</v>
+        <v>271</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>271</v>
+        <v>160</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>272</v>
+        <v>35</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
@@ -4239,37 +4163,37 @@
         <v>273</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>189</v>
+        <v>44</v>
       </c>
       <c r="J67" s="3">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B68" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="B68" s="3" t="s">
-        <v>275</v>
-      </c>
       <c r="C68" s="3" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>135</v>
+        <v>35</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>69</v>
+        <v>169</v>
       </c>
       <c r="J68" s="3">
         <v>0</v>
@@ -4277,32 +4201,32 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>169</v>
+        <v>276</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>277</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>278</v>
+        <v>160</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>135</v>
+        <v>35</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="I69" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="I69" s="3" t="s">
-        <v>189</v>
-      </c>
       <c r="J69" s="3">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="70">
@@ -4310,997 +4234,849 @@
         <v>280</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>281</v>
+        <v>167</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>223</v>
+        <v>160</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>69</v>
+        <v>233</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>64</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="C71" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="C71" s="3" t="s">
-        <v>285</v>
-      </c>
       <c r="D71" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F71" s="3"/>
       <c r="G71" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J71" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>288</v>
-      </c>
       <c r="C72" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D72" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E72" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="I72" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>290</v>
-      </c>
       <c r="J72" s="3">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="B73" s="3" t="s">
-        <v>292</v>
-      </c>
       <c r="C73" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="I73" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="I73" s="3" t="s">
-        <v>294</v>
-      </c>
       <c r="J73" s="3">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D74" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E74" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="E74" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="F74" s="3"/>
       <c r="G74" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="J74" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="B75" s="3" t="s">
-        <v>298</v>
-      </c>
       <c r="C75" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F75" s="3"/>
       <c r="G75" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J75" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>300</v>
+        <v>182</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F76" s="3"/>
       <c r="G76" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J76" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>69</v>
+        <v>165</v>
       </c>
       <c r="J77" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D78" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E78" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="J78" s="3">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D79" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E79" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="J79" s="3">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C80" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="B80" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>316</v>
-      </c>
       <c r="D80" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>318</v>
+        <v>238</v>
       </c>
       <c r="J80" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>320</v>
+        <v>182</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>271</v>
+        <v>299</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>272</v>
+        <v>131</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>98</v>
+        <v>318</v>
       </c>
       <c r="J81" s="3">
-        <v>6</v>
+        <v>45</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>324</v>
+        <v>177</v>
       </c>
       <c r="J82" s="3">
-        <v>44</v>
+        <v>3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>284</v>
+        <v>322</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>285</v>
+        <v>48</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>135</v>
+        <v>35</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="J83" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>277</v>
+        <v>325</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>328</v>
+        <v>183</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>257</v>
+        <v>35</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="J84" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>331</v>
+        <v>266</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>223</v>
+        <v>328</v>
       </c>
       <c r="D85" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E85" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>84</v>
+        <v>204</v>
       </c>
       <c r="J85" s="3">
-        <v>34</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>333</v>
+        <v>40</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>334</v>
+        <v>236</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>335</v>
+        <v>160</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>336</v>
+        <v>35</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="J86" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>135</v>
+        <v>35</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>98</v>
+        <v>258</v>
       </c>
       <c r="J87" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="E88" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="B88" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E88" s="3" t="s">
-        <v>42</v>
       </c>
       <c r="F88" s="3"/>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>88</v>
+        <v>318</v>
       </c>
       <c r="J88" s="3">
-        <v>27</v>
+        <v>45</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>164</v>
+        <v>338</v>
       </c>
       <c r="D89" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E89" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>247</v>
+        <v>169</v>
       </c>
       <c r="J89" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>180</v>
+        <v>251</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>201</v>
+        <v>252</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>202</v>
+        <v>253</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F90" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>341</v>
+      </c>
       <c r="G90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>324</v>
+        <v>343</v>
       </c>
       <c r="J90" s="3">
-        <v>44</v>
+        <v>25</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>348</v>
+        <v>40</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>222</v>
+        <v>344</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>223</v>
+        <v>194</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>36</v>
+        <v>195</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>69</v>
+        <v>120</v>
       </c>
       <c r="J91" s="3">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>255</v>
+        <v>347</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>256</v>
+        <v>160</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>257</v>
+        <v>35</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="G92" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>353</v>
+        <v>214</v>
       </c>
       <c r="J92" s="3">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E93" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B93" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="C93" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="E93" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F93" s="3"/>
+      <c r="F93" s="3" t="s">
+        <v>351</v>
+      </c>
       <c r="G93" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>124</v>
+        <v>289</v>
       </c>
       <c r="J93" s="3">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>357</v>
+        <v>222</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D94" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E94" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>358</v>
-      </c>
+      <c r="F94" s="3"/>
       <c r="G94" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>220</v>
+        <v>355</v>
       </c>
       <c r="J94" s="3">
-        <v>41</v>
+        <v>14</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>362</v>
+        <v>183</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>135</v>
+        <v>35</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>132</v>
+        <v>204</v>
       </c>
       <c r="J95" s="3">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>49</v>
+        <v>206</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>52</v>
+        <v>165</v>
       </c>
       <c r="J96" s="3">
-        <v>28</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>232</v>
+        <v>174</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D97" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E97" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>37</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>369</v>
+        <v>169</v>
       </c>
       <c r="J97" s="3">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="B98" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="C98" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E98" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F98" s="3"/>
-      <c r="G98" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="I98" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="J98" s="3">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="B99" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E99" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F99" s="3"/>
-      <c r="G99" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H99" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="I99" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="J99" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="B100" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="C100" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F100" s="3"/>
-      <c r="G100" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="J100" s="3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F101" s="3"/>
-      <c r="G101" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="J101" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B102" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="C102" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F102" s="3"/>
-      <c r="G102" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="J102" s="3">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J102"/>
+  <autoFilter ref="A1:J97"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5398,11 +5174,6 @@
     <hyperlink ref="H95" r:id="rId94"/>
     <hyperlink ref="H96" r:id="rId95"/>
     <hyperlink ref="H97" r:id="rId96"/>
-    <hyperlink ref="H98" r:id="rId97"/>
-    <hyperlink ref="H99" r:id="rId98"/>
-    <hyperlink ref="H100" r:id="rId99"/>
-    <hyperlink ref="H101" r:id="rId100"/>
-    <hyperlink ref="H102" r:id="rId101"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5411,7 +5182,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5421,55 +5192,55 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>27</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>67</v>
+        <v>166</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>63</v>
+        <v>167</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>36</v>
+        <v>160</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>68</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5477,18 +5248,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>49</v>
+        <v>198</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5496,18 +5267,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>171</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>41</v>
+        <v>170</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>183</v>
+        <v>234</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>49</v>
+        <v>194</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5515,18 +5286,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>184</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>204</v>
+        <v>274</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>49</v>
+        <v>183</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5534,18 +5305,18 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>205</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>221</v>
+        <v>321</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>222</v>
+        <v>322</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>223</v>
+        <v>48</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -5553,18 +5324,18 @@
         <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>224</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>274</v>
+        <v>324</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>275</v>
+        <v>325</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -5572,18 +5343,18 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>276</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>280</v>
+        <v>336</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>281</v>
+        <v>337</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>223</v>
+        <v>338</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -5591,18 +5362,18 @@
         <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>282</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>303</v>
+        <v>362</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>304</v>
+        <v>174</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>285</v>
+        <v>160</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5610,49 +5381,11 @@
         <v>22</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>381</v>
+        <v>363</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G12"/>
+  <autoFilter ref="A1:G10"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
@@ -5663,8 +5396,6 @@
     <hyperlink ref="G8" r:id="rId7"/>
     <hyperlink ref="G9" r:id="rId8"/>
     <hyperlink ref="G10" r:id="rId9"/>
-    <hyperlink ref="G11" r:id="rId10"/>
-    <hyperlink ref="G12" r:id="rId11"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5678,15 +5409,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>385</v>
+        <v>364</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>386</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="B2" s="3">
         <v>20</v>
@@ -5694,7 +5425,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>181</v>
+        <v>351</v>
       </c>
       <c r="B3" s="3">
         <v>20</v>
@@ -5702,7 +5433,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>388</v>
+        <v>367</v>
       </c>
       <c r="B4" s="3">
         <v>18</v>
@@ -5710,7 +5441,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>389</v>
+        <v>368</v>
       </c>
       <c r="B5" s="3">
         <v>17</v>
@@ -5718,7 +5449,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>390</v>
+        <v>369</v>
       </c>
       <c r="B6" s="3">
         <v>13</v>
@@ -5726,7 +5457,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>391</v>
+        <v>370</v>
       </c>
       <c r="B7" s="3">
         <v>13</v>
@@ -5734,7 +5465,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>392</v>
+        <v>371</v>
       </c>
       <c r="B8" s="3">
         <v>12</v>
@@ -5742,7 +5473,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>393</v>
+        <v>372</v>
       </c>
       <c r="B9" s="3">
         <v>12</v>
@@ -5750,7 +5481,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>394</v>
+        <v>373</v>
       </c>
       <c r="B10" s="3">
         <v>12</v>
@@ -5758,7 +5489,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
@@ -5766,7 +5497,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>395</v>
+        <v>374</v>
       </c>
       <c r="B12" s="3">
         <v>9</v>
@@ -5774,7 +5505,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>396</v>
+        <v>375</v>
       </c>
       <c r="B13" s="3">
         <v>8</v>
@@ -5782,7 +5513,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>397</v>
+        <v>376</v>
       </c>
       <c r="B14" s="3">
         <v>7</v>
@@ -5790,7 +5521,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>398</v>
+        <v>377</v>
       </c>
       <c r="B15" s="3">
         <v>7</v>
@@ -5798,7 +5529,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>399</v>
+        <v>378</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -5817,23 +5548,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>400</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B2" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B3" s="3">
         <v>5</v>
@@ -5841,15 +5572,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>35</v>
+        <v>167</v>
       </c>
       <c r="B4" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>114</v>
+        <v>34</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -5857,7 +5588,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5865,7 +5596,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>232</v>
+        <v>174</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5873,23 +5604,23 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>54</v>
+        <v>182</v>
       </c>
       <c r="B8" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>126</v>
+        <v>222</v>
       </c>
       <c r="B9" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>173</v>
+        <v>53</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5897,7 +5628,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>222</v>
+        <v>122</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5905,7 +5636,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>255</v>
+        <v>216</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5913,7 +5644,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>277</v>
+        <v>236</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5921,7 +5652,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>284</v>
+        <v>251</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5929,7 +5660,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>300</v>
+        <v>266</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5937,10 +5668,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>48</v>
+        <v>283</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5951,23 +5682,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>401</v>
+        <v>380</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>402</v>
+        <v>381</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>400</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2">
@@ -5975,13 +5706,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C2" s="3">
-        <v>35.8</v>
+        <v>26.9</v>
       </c>
       <c r="D2" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -5989,7 +5720,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C3" s="3">
         <v>23.8</v>
@@ -6003,7 +5734,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C4" s="3">
         <v>10.9</v>
@@ -6017,7 +5748,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C5" s="3">
         <v>10.1</v>
@@ -6031,7 +5762,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C6" s="3">
         <v>5.0</v>
@@ -6045,13 +5776,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="C7" s="3">
-        <v>4.0</v>
+        <v>4.8</v>
       </c>
       <c r="D7" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -6059,7 +5790,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C8" s="3">
         <v>3.6</v>
@@ -6073,7 +5804,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>232</v>
+        <v>174</v>
       </c>
       <c r="C9" s="3">
         <v>3.6</v>
@@ -6087,13 +5818,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>48</v>
+        <v>182</v>
       </c>
       <c r="C10" s="3">
-        <v>3.0</v>
+        <v>3.6</v>
       </c>
       <c r="D10" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -6101,13 +5832,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>255</v>
+        <v>222</v>
       </c>
       <c r="C11" s="3">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="D11" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -6115,10 +5846,10 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>140</v>
+        <v>47</v>
       </c>
       <c r="C12" s="3">
-        <v>2.6</v>
+        <v>3.0</v>
       </c>
       <c r="D12" s="3">
         <v>1</v>
@@ -6129,13 +5860,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>145</v>
+        <v>251</v>
       </c>
       <c r="C13" s="3">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="D13" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -6143,10 +5874,10 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>173</v>
+        <v>236</v>
       </c>
       <c r="C14" s="3">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="D14" s="3">
         <v>2</v>
@@ -6157,13 +5888,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>222</v>
+        <v>136</v>
       </c>
       <c r="C15" s="3">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="D15" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -6171,13 +5902,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>277</v>
+        <v>141</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
       </c>
       <c r="D16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6194,46 +5925,46 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>403</v>
+        <v>382</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>404</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>405</v>
+        <v>384</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>406</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B3" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>407</v>
+        <v>386</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="3">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>408</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -6249,65 +5980,57 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>403</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B2" s="3">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B3" s="3">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>187</v>
+        <v>253</v>
       </c>
       <c r="B5" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>257</v>
+        <v>212</v>
       </c>
       <c r="B6" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="B7" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="B8" s="3">
         <v>1</v>
       </c>
     </row>
@@ -6332,34 +6055,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>401</v>
+        <v>380</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>409</v>
+        <v>388</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>410</v>
+        <v>389</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>411</v>
+        <v>390</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2">
@@ -6367,31 +6090,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>412</v>
+        <v>391</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>413</v>
+        <v>392</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>414</v>
+        <v>393</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>415</v>
+        <v>394</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>416</v>
+        <v>395</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>417</v>
+        <v>396</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3">
@@ -6399,31 +6122,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>418</v>
+        <v>397</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>419</v>
+        <v>398</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>271</v>
+        <v>160</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>420</v>
+        <v>399</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>422</v>
+        <v>401</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>84</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4">
@@ -6431,31 +6154,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>423</v>
+        <v>403</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>424</v>
+        <v>404</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>164</v>
+        <v>260</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>426</v>
+        <v>406</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>428</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5">
@@ -6463,31 +6186,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>429</v>
+        <v>408</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>430</v>
+        <v>409</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>415</v>
+        <v>394</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>431</v>
+        <v>410</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>432</v>
+        <v>411</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6">
@@ -6495,31 +6218,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>433</v>
+        <v>412</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>434</v>
+        <v>413</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>415</v>
+        <v>394</v>
       </c>
       <c r="F6" s="3">
         <v>80</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>435</v>
+        <v>414</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>436</v>
+        <v>415</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>437</v>
+        <v>416</v>
       </c>
     </row>
     <row r="7">
@@ -6527,31 +6250,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>438</v>
+        <v>417</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>439</v>
+        <v>418</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>328</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="F7" s="3">
         <v>70</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>440</v>
+        <v>419</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>441</v>
+        <v>420</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
@@ -6559,31 +6282,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>442</v>
+        <v>421</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>443</v>
+        <v>422</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>444</v>
+        <v>423</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>415</v>
+        <v>394</v>
       </c>
       <c r="F8" s="3">
         <v>68</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>445</v>
+        <v>424</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>446</v>
+        <v>425</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>447</v>
+        <v>426</v>
       </c>
     </row>
     <row r="9">
@@ -6591,31 +6314,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>448</v>
+        <v>427</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>449</v>
+        <v>428</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>450</v>
+        <v>429</v>
       </c>
       <c r="F9" s="3">
         <v>61</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>451</v>
+        <v>430</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>452</v>
+        <v>431</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
@@ -6623,31 +6346,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>453</v>
+        <v>432</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>415</v>
+        <v>394</v>
       </c>
       <c r="F10" s="3">
         <v>60</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>454</v>
+        <v>433</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>455</v>
+        <v>434</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="11">
@@ -6655,31 +6378,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>456</v>
+        <v>435</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>457</v>
+        <v>436</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>450</v>
+        <v>429</v>
       </c>
       <c r="F11" s="3">
         <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>458</v>
+        <v>437</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>459</v>
+        <v>438</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
     </row>
     <row r="12">
@@ -6687,31 +6410,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>460</v>
+        <v>439</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>461</v>
+        <v>440</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>462</v>
+        <v>441</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>450</v>
+        <v>429</v>
       </c>
       <c r="F12" s="3">
         <v>47</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>463</v>
+        <v>442</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>464</v>
+        <v>443</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -6719,31 +6442,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>465</v>
+        <v>444</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>466</v>
+        <v>445</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>467</v>
+        <v>446</v>
       </c>
       <c r="F13" s="3">
         <v>46</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>468</v>
+        <v>447</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>469</v>
+        <v>448</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14">
@@ -6751,31 +6474,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>376</v>
+        <v>449</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>470</v>
+        <v>450</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>186</v>
+        <v>211</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>415</v>
+        <v>394</v>
       </c>
       <c r="F14" s="3">
         <v>44</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>471</v>
+        <v>451</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>472</v>
+        <v>452</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15">
@@ -6783,31 +6506,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>473</v>
+        <v>453</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>474</v>
+        <v>454</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="F15" s="3">
         <v>39</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>475</v>
+        <v>455</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>476</v>
+        <v>456</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6815,31 +6538,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>477</v>
+        <v>457</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>478</v>
+        <v>458</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>415</v>
+        <v>394</v>
       </c>
       <c r="F16" s="3">
         <v>36</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>479</v>
+        <v>459</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>481</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17">
@@ -6847,31 +6570,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>482</v>
+        <v>461</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>483</v>
+        <v>462</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>335</v>
+        <v>463</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>415</v>
+        <v>394</v>
       </c>
       <c r="F17" s="3">
         <v>32</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>484</v>
+        <v>464</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>485</v>
+        <v>465</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18">
@@ -6879,31 +6602,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>477</v>
+        <v>457</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>486</v>
+        <v>466</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>415</v>
+        <v>394</v>
       </c>
       <c r="F18" s="3">
         <v>28</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>487</v>
+        <v>467</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>488</v>
+        <v>468</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="19">
@@ -6911,31 +6634,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>489</v>
+        <v>469</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>225</v>
+        <v>470</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>186</v>
+        <v>211</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>450</v>
+        <v>429</v>
       </c>
       <c r="F19" s="3">
         <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>490</v>
+        <v>471</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>491</v>
+        <v>472</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="20">
@@ -6943,31 +6666,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>492</v>
+        <v>473</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>493</v>
+        <v>322</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>494</v>
+        <v>48</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>450</v>
+        <v>394</v>
       </c>
       <c r="F20" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>495</v>
+        <v>474</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>496</v>
+        <v>475</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21">
@@ -6975,31 +6698,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>497</v>
+        <v>457</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>498</v>
+        <v>476</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>49</v>
+        <v>175</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>415</v>
+        <v>394</v>
       </c>
       <c r="F21" s="3">
         <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>499</v>
+        <v>477</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>500</v>
+        <v>478</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>40</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W39.xlsx
+++ b/reports/devops-jobs-israel-2026-W39.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="490">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24T11:35:11</t>
+    <t xml:space="preserve">2026-09-25T11:41:46</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -456,21 +456,6 @@
     <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
   </si>
   <si>
-    <t xml:space="preserve">DevOps Lead (FedRAMP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orcasecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Helm, Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://orca.security/about/careers/6149333004?gh_jid=6149333004</t>
-  </si>
-  <si>
     <t xml:space="preserve">Site Reliability Team Leader</t>
   </si>
   <si>
@@ -510,6 +495,21 @@
     <t xml:space="preserve">2026-08-07</t>
   </si>
   <si>
+    <t xml:space="preserve">Sr. Principal, DevOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parallel Wireless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-principal-devops-at-parallel-wireless-4468461559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-21</t>
+  </si>
+  <si>
     <t xml:space="preserve">Radware</t>
   </si>
   <si>
@@ -519,90 +519,81 @@
     <t xml:space="preserve">2026-09-23</t>
   </si>
   <si>
-    <t xml:space="preserve">Principal DevOps Engineer</t>
+    <t xml:space="preserve">DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CommBox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commbox-4470453217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform DevOps Engineer - Core Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jeen.ai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-core-platform-at-jeen-ai-4469586881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Play Perfect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4469727405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nayax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nayax-4469432294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4451477598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software Engineer (DevOps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akamai Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-akamai-technologies-4461033122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connecteam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pagaya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pagaya-4316888825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer (Secrets Manager)</t>
   </si>
   <si>
     <t xml:space="preserve">Palo Alto Networks</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-at-palo-alto-networks-4469323268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CommBox</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-commbox-4470453217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform DevOps Engineer - Core Platform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeen.ai</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-core-platform-at-jeen-ai-4469586881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Play Perfect</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4469727405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nayax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nayax-4469432294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-nvidia-4451477598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software Engineer (DevOps)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akamai Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-akamai-technologies-4461033122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pagaya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-pagaya-4316888825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Secrets Manager)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
   </si>
   <si>
@@ -666,6 +657,27 @@
     <t xml:space="preserve">2026-08-13</t>
   </si>
   <si>
+    <t xml:space="preserve">Sr Staff DevOps Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-staff-devops-platform-engineer-at-palo-alto-networks-4419603015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI First DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomorrow.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-first-devops-engineer-at-tomorrow-io-4469679411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-25</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps Engineer 4218</t>
   </si>
   <si>
@@ -675,6 +687,15 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-4218-at-bank-hapoalim-%D7%91%D7%A0%D7%A7-%D7%94%D7%A4%D7%95%D7%A2%D7%9C%D7%99%D7%9D-4469435452</t>
   </si>
   <si>
+    <t xml:space="preserve">Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gloat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gloat-4471492397</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cellebrite</t>
   </si>
   <si>
@@ -696,9 +717,6 @@
     <t xml:space="preserve">2026-08-24</t>
   </si>
   <si>
-    <t xml:space="preserve">Devops Engineer</t>
-  </si>
-  <si>
     <t xml:space="preserve">ZyG</t>
   </si>
   <si>
@@ -753,12 +771,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4464286063</t>
   </si>
   <si>
-    <t xml:space="preserve">EasySend</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-easysend-4467548799</t>
-  </si>
-  <si>
     <t xml:space="preserve">DevOps Engineer III</t>
   </si>
   <si>
@@ -771,7 +783,223 @@
     <t xml:space="preserve">2026-07-17</t>
   </si>
   <si>
-    <t xml:space="preserve">GenAI Group DevOps Engineer</t>
+    <t xml:space="preserve">Stealth Startup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-stealth-startup-4468441366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AllCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4470273860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-confidential-careers-4468585946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lod, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4468557198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer 4210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-4210-at-bank-hapoalim-%D7%91%D7%A0%D7%A7-%D7%94%D7%A4%D7%95%D7%A2%D7%9C%D7%99%D7%9D-4469434426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monday.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-jobgether-4468712370</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DRW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441563717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IgniteTech</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VP, Site Reliability Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/vp-site-reliability-engineering-at-oracle-4459580128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manager, Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crusoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-production-engineering-at-crusoe-4442593613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARMAN International</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-dt-4452913774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-jobgether-4468496644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Data Infrastructure Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-team-leader-at-evoke-4470918616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-sqlink-group-4468564839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software and DevOps Engineer, DOCA Verification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-and-devops-engineer-doca-verification-at-nvidia-4404223687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal Platform Engineer - Devops (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-platform-engineer-devops-cortex-at-palo-alto-networks-4459956703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Research Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4466990468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer - Azure &amp; AWS</t>
   </si>
   <si>
     <t xml:space="preserve">Elbit Systems Israel</t>
@@ -780,270 +1008,6 @@
     <t xml:space="preserve">Haifa District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/genai-group-devops-engineer-at-elbit-systems-israel-4395652910</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealth Startup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-stealth-startup-4468441366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AllCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4470273860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-confidential-careers-4468585946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lod, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4468557198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer 4210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-4210-at-bank-hapoalim-%D7%91%D7%A0%D7%A7-%D7%94%D7%A4%D7%95%D7%A2%D7%9C%D7%99%D7%9D-4469434426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealth Company</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-stealth-company-4468995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wix</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-at-wix-4464485443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-jobgether-4468712370</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IgniteTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VP, Site Reliability Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/vp-site-reliability-engineering-at-oracle-4459580128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-nvidia-4458308805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Director, Site Reliability Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DuckDuckGo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/director-site-reliability-engineering-at-duckduckgo-4469057695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Production Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rhino Federated Computing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-production-engineer-at-rhino-federated-computing-4430658019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-06-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manager, Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crusoe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-production-engineering-at-crusoe-4442593613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HARMAN International</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-jobgether-4468496644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Data Infrastructure Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-team-leader-at-evoke-4470918616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Database Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sharpies PRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/database-reliability-engineer-at-sharpies-pro-4469456732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-sqlink-group-4468564839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-fiverr-4458388230</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sr Staff DevOps Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-staff-devops-platform-engineer-at-palo-alto-networks-4419603015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TeraCyte Analytics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-devops-engineer-at-teracyte-analytics-4469729261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer - Azure &amp; AWS</t>
-  </si>
-  <si>
     <t xml:space="preserve">AWS, Azure</t>
   </si>
   <si>
@@ -1053,12 +1017,6 @@
     <t xml:space="preserve">2026-08-30</t>
   </si>
   <si>
-    <t xml:space="preserve">TeraSky</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-terasky-4455198528</t>
-  </si>
-  <si>
     <t xml:space="preserve">Senior MLOps Platform Engineer - QuantumBlack, AI by McKinsey</t>
   </si>
   <si>
@@ -1071,12 +1029,30 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-mlops-platform-engineer-quantumblack-ai-by-mckinsey-at-quantumblack-ai-by-mckinsey-4423517900</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior Staff DevOps Engineer - Cloud Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-cloud-security-at-palo-alto-networks-4450813194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Cloud Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genpact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-team-lead-at-genpact-4469756686</t>
+  </si>
+  <si>
     <t xml:space="preserve">Semperis</t>
   </si>
   <si>
-    <t xml:space="preserve">Security</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-security-engineer-at-semperis-4438770193</t>
   </si>
   <si>
@@ -1134,27 +1110,27 @@
     <t xml:space="preserve">GCP</t>
   </si>
   <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
     <t xml:space="preserve">Terraform</t>
   </si>
   <si>
     <t xml:space="preserve">Azure</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
     <t xml:space="preserve">Networking</t>
   </si>
   <si>
+    <t xml:space="preserve">Argo CD</t>
+  </si>
+  <si>
     <t xml:space="preserve">Helm</t>
   </si>
   <si>
-    <t xml:space="preserve">Argo CD</t>
-  </si>
-  <si>
     <t xml:space="preserve">WAF/CDN</t>
   </si>
   <si>
@@ -1179,10 +1155,10 @@
     <t xml:space="preserve">0%</t>
   </si>
   <si>
-    <t xml:space="preserve">47.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.1%</t>
+    <t xml:space="preserve">46.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.8%</t>
   </si>
   <si>
     <t xml:space="preserve">Role</t>
@@ -1269,9 +1245,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
     <t xml:space="preserve">Software Engineer Student, SPIV team</t>
   </si>
   <si>
@@ -1317,15 +1290,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Analyst | Splunk &amp; Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-splunk-infrastructure-at-confidential-careers-4465957826</t>
-  </si>
-  <si>
     <t xml:space="preserve">Technical Support Specialist</t>
   </si>
   <si>
@@ -1380,6 +1344,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-tytocare-4461579939</t>
   </si>
   <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shavit Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-shavit-software-4470938821</t>
+  </si>
+  <si>
     <t xml:space="preserve">Software Engineering INTERN</t>
   </si>
   <si>
@@ -1404,21 +1383,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator 7992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sysnet part of Amanet Tec</t>
-  </si>
-  <si>
-    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Cloud (any), Virtualization, Active Directory, Windows Server, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-7992-at-sysnet-part-of-amanet-tec-4467053868</t>
-  </si>
-  <si>
     <t xml:space="preserve">Gini-Apps</t>
   </si>
   <si>
@@ -1440,6 +1404,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior Field Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mornex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hadera, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Networking, Monitoring, Virtualization, Active Directory, Windows Server, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-field-support-engineer-at-mornex-4457946363</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
   </si>
   <si>
@@ -1449,13 +1428,16 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
   </si>
   <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441078871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-16</t>
   </si>
   <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
@@ -1464,10 +1446,10 @@
     <t xml:space="preserve">Roles requiring it</t>
   </si>
   <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
     <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
     <t xml:space="preserve">Cloud (any)</t>
@@ -1631,7 +1613,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7">
@@ -1639,7 +1621,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -1647,7 +1629,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9">
@@ -1655,7 +1637,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>928</v>
+        <v>933</v>
       </c>
     </row>
     <row r="10">
@@ -1727,7 +1709,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
@@ -1735,7 +1717,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1754,20 +1736,20 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="B2" s="3">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="B3" s="3">
         <v>7</v>
@@ -1775,23 +1757,23 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>399</v>
+        <v>473</v>
       </c>
       <c r="B5" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>446</v>
+        <v>391</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1799,7 +1781,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>479</v>
+        <v>434</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1818,23 +1800,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="B3" s="3">
         <v>18</v>
@@ -1842,31 +1824,31 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="B4" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="B5" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="B6" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="B7" s="3">
         <v>12</v>
@@ -1874,7 +1856,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="B8" s="3">
         <v>11</v>
@@ -1882,7 +1864,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
@@ -1890,7 +1872,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
@@ -1898,15 +1880,15 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="B11" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>372</v>
+        <v>358</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -1914,15 +1896,15 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B13" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -1930,7 +1912,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
@@ -1938,7 +1920,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -1966,13 +1948,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
     </row>
     <row r="2">
@@ -1980,13 +1962,13 @@
         <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2" s="3">
-        <v>12.9</v>
+        <v>13.6</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1995,88 +1977,88 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C3" s="3">
-        <v>39.1</v>
+        <v>35.7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>9.8</v>
+        <v>8.6</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>32.9</v>
+        <v>30.8</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>15.5</v>
+        <v>15.8</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>21.1</v>
+        <v>21.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2160,7 +2142,7 @@
         <v>39</v>
       </c>
       <c r="J2" s="3">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -2192,7 +2174,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
@@ -2224,7 +2206,7 @@
         <v>44</v>
       </c>
       <c r="J4" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="5">
@@ -2256,7 +2238,7 @@
         <v>51</v>
       </c>
       <c r="J5" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6">
@@ -2288,7 +2270,7 @@
         <v>57</v>
       </c>
       <c r="J6" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
@@ -2320,7 +2302,7 @@
         <v>44</v>
       </c>
       <c r="J7" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
@@ -2352,7 +2334,7 @@
         <v>65</v>
       </c>
       <c r="J8" s="3">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9">
@@ -2384,7 +2366,7 @@
         <v>69</v>
       </c>
       <c r="J9" s="3">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -2416,7 +2398,7 @@
         <v>73</v>
       </c>
       <c r="J10" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -2448,7 +2430,7 @@
         <v>76</v>
       </c>
       <c r="J11" s="3">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12">
@@ -2480,7 +2462,7 @@
         <v>80</v>
       </c>
       <c r="J12" s="3">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -2512,7 +2494,7 @@
         <v>84</v>
       </c>
       <c r="J13" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14">
@@ -2544,7 +2526,7 @@
         <v>88</v>
       </c>
       <c r="J14" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -2576,7 +2558,7 @@
         <v>94</v>
       </c>
       <c r="J15" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -2608,7 +2590,7 @@
         <v>98</v>
       </c>
       <c r="J16" s="3">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17">
@@ -2640,7 +2622,7 @@
         <v>88</v>
       </c>
       <c r="J17" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -2672,7 +2654,7 @@
         <v>57</v>
       </c>
       <c r="J18" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19">
@@ -2704,7 +2686,7 @@
         <v>108</v>
       </c>
       <c r="J19" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -2736,7 +2718,7 @@
         <v>84</v>
       </c>
       <c r="J20" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21">
@@ -2768,7 +2750,7 @@
         <v>117</v>
       </c>
       <c r="J21" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22">
@@ -2800,7 +2782,7 @@
         <v>120</v>
       </c>
       <c r="J22" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23">
@@ -2832,7 +2814,7 @@
         <v>125</v>
       </c>
       <c r="J23" s="3">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24">
@@ -2864,7 +2846,7 @@
         <v>128</v>
       </c>
       <c r="J24" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25">
@@ -2896,7 +2878,7 @@
         <v>134</v>
       </c>
       <c r="J25" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26">
@@ -2928,7 +2910,7 @@
         <v>139</v>
       </c>
       <c r="J26" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="27">
@@ -2960,7 +2942,7 @@
         <v>44</v>
       </c>
       <c r="J27" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28">
@@ -2971,36 +2953,36 @@
         <v>146</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>65</v>
+        <v>148</v>
       </c>
       <c r="J28" s="3">
-        <v>24</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>151</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>35</v>
@@ -3012,7 +2994,7 @@
         <v>36</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>23</v>
@@ -3024,44 +3006,42 @@
         <v>153</v>
       </c>
       <c r="J29" s="3">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="C30" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="D30" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F30" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H30" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H30" s="3" t="s">
+      <c r="I30" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="I30" s="3" t="s">
-        <v>158</v>
-      </c>
       <c r="J30" s="3">
-        <v>17</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>40</v>
+        <v>158</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>159</v>
@@ -3070,7 +3050,7 @@
         <v>160</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>35</v>
+        <v>131</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>41</v>
@@ -3086,7 +3066,7 @@
         <v>162</v>
       </c>
       <c r="J31" s="3">
-        <v>48</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32">
@@ -3097,7 +3077,7 @@
         <v>163</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>35</v>
@@ -3116,7 +3096,7 @@
         <v>165</v>
       </c>
       <c r="J32" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -3127,13 +3107,13 @@
         <v>167</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>160</v>
+        <v>48</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
@@ -3143,24 +3123,24 @@
         <v>168</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="J33" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="C34" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="D34" s="3" t="s">
-        <v>35</v>
+        <v>131</v>
       </c>
       <c r="E34" s="3" t="s">
         <v>36</v>
@@ -3173,40 +3153,40 @@
         <v>172</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="J34" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="C35" s="3" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="J35" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -3214,10 +3194,10 @@
         <v>40</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>160</v>
+        <v>48</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>35</v>
@@ -3230,13 +3210,13 @@
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="J36" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -3244,10 +3224,10 @@
         <v>40</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>48</v>
+        <v>179</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>35</v>
@@ -3260,24 +3240,24 @@
         <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>165</v>
+        <v>44</v>
       </c>
       <c r="J37" s="3">
-        <v>1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>40</v>
+        <v>181</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>182</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>35</v>
@@ -3290,54 +3270,54 @@
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="J38" s="3">
-        <v>44</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="J39" s="3">
-        <v>24</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>35</v>
@@ -3350,60 +3330,60 @@
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>108</v>
+        <v>188</v>
       </c>
       <c r="J40" s="3">
-        <v>27</v>
+        <v>74</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>170</v>
+        <v>189</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>190</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>160</v>
+        <v>191</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>35</v>
+        <v>192</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>192</v>
+        <v>157</v>
       </c>
       <c r="J41" s="3">
-        <v>73</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>193</v>
+        <v>166</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>195</v>
+        <v>35</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
@@ -3413,21 +3393,21 @@
         <v>196</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="J42" s="3">
-        <v>48</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>197</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>198</v>
+        <v>48</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>35</v>
@@ -3440,27 +3420,27 @@
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>48</v>
+        <v>171</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>35</v>
+        <v>131</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>36</v>
@@ -3470,57 +3450,57 @@
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="I44" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="J44" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>170</v>
+        <v>40</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>202</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>175</v>
+        <v>203</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J45" s="3">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>40</v>
+        <v>206</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>35</v>
+        <v>209</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>41</v>
@@ -3530,27 +3510,27 @@
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="J46" s="3">
-        <v>30</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="E47" s="3" t="s">
         <v>41</v>
@@ -3566,7 +3546,7 @@
         <v>214</v>
       </c>
       <c r="J47" s="3">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="48">
@@ -3577,7 +3557,7 @@
         <v>216</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>35</v>
@@ -3593,37 +3573,37 @@
         <v>217</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>165</v>
+        <v>218</v>
       </c>
       <c r="J48" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>40</v>
+        <v>219</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>195</v>
+        <v>35</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>204</v>
+        <v>165</v>
       </c>
       <c r="J49" s="3">
         <v>2</v>
@@ -3631,106 +3611,106 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>40</v>
+        <v>222</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>206</v>
+        <v>155</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="J50" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>170</v>
+        <v>40</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>160</v>
+        <v>191</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>35</v>
+        <v>192</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>224</v>
+        <v>201</v>
       </c>
       <c r="J51" s="3">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>225</v>
+        <v>40</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>160</v>
+        <v>203</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="J52" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>228</v>
+        <v>166</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>174</v>
+        <v>229</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="E53" s="3" t="s">
         <v>36</v>
@@ -3740,24 +3720,24 @@
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>177</v>
+        <v>231</v>
       </c>
       <c r="J53" s="3">
-        <v>3</v>
+        <v>32</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>35</v>
@@ -3770,27 +3750,27 @@
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="J54" s="3">
-        <v>64</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B55" s="3" t="s">
-        <v>234</v>
-      </c>
       <c r="C55" s="3" t="s">
-        <v>194</v>
+        <v>171</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>195</v>
+        <v>131</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>36</v>
@@ -3803,21 +3783,21 @@
         <v>235</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="J55" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>170</v>
+        <v>236</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>35</v>
@@ -3830,27 +3810,27 @@
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J56" s="3">
-        <v>43</v>
+        <v>65</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>131</v>
+        <v>192</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>36</v>
@@ -3860,24 +3840,24 @@
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>241</v>
+        <v>175</v>
       </c>
       <c r="J57" s="3">
-        <v>11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>242</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>35</v>
@@ -3893,51 +3873,51 @@
         <v>243</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="J58" s="3">
-        <v>11</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>40</v>
+        <v>166</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>35</v>
+        <v>131</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>128</v>
+        <v>247</v>
       </c>
       <c r="J59" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>246</v>
+        <v>166</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>35</v>
@@ -3950,13 +3930,13 @@
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J60" s="3">
-        <v>69</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61">
@@ -3967,10 +3947,10 @@
         <v>251</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>252</v>
+        <v>155</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>253</v>
+        <v>35</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>36</v>
@@ -3980,13 +3960,13 @@
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="J61" s="3">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="62">
@@ -3994,10 +3974,10 @@
         <v>40</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>131</v>
@@ -4010,27 +3990,27 @@
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="J62" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B63" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="D63" s="3" t="s">
         <v>259</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>261</v>
       </c>
       <c r="E63" s="3" t="s">
         <v>36</v>
@@ -4040,24 +4020,24 @@
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="J63" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>131</v>
@@ -4070,24 +4050,24 @@
         <v>22</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="I64" s="3" t="s">
         <v>165</v>
       </c>
       <c r="J64" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>131</v>
@@ -4100,24 +4080,24 @@
         <v>22</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="J65" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>35</v>
@@ -4130,24 +4110,24 @@
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>165</v>
       </c>
       <c r="J66" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>35</v>
@@ -4160,57 +4140,57 @@
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="I67" s="3" t="s">
         <v>44</v>
       </c>
       <c r="J67" s="3">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>170</v>
+        <v>272</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>274</v>
+        <v>190</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>169</v>
+        <v>239</v>
       </c>
       <c r="J68" s="3">
-        <v>0</v>
+        <v>65</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C69" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="D69" s="3" t="s">
-        <v>35</v>
+        <v>131</v>
       </c>
       <c r="E69" s="3" t="s">
         <v>41</v>
@@ -4220,57 +4200,57 @@
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>279</v>
+        <v>162</v>
       </c>
       <c r="J69" s="3">
-        <v>16</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>167</v>
+        <v>279</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="I70" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="I70" s="3" t="s">
-        <v>233</v>
-      </c>
       <c r="J70" s="3">
-        <v>64</v>
+        <v>42</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="B71" s="3" t="s">
-        <v>283</v>
-      </c>
       <c r="C71" s="3" t="s">
-        <v>284</v>
+        <v>191</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>131</v>
+        <v>192</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>41</v>
@@ -4280,87 +4260,87 @@
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>177</v>
+        <v>284</v>
       </c>
       <c r="J71" s="3">
-        <v>3</v>
+        <v>61</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="B72" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="B72" s="3" t="s">
-        <v>287</v>
-      </c>
       <c r="C72" s="3" t="s">
-        <v>160</v>
+        <v>276</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>35</v>
+        <v>131</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F72" s="3"/>
       <c r="G72" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="I72" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>289</v>
-      </c>
       <c r="J72" s="3">
-        <v>41</v>
+        <v>68</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>291</v>
+        <v>229</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>284</v>
+        <v>155</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F73" s="3"/>
       <c r="G73" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>293</v>
+        <v>80</v>
       </c>
       <c r="J73" s="3">
-        <v>67</v>
+        <v>36</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>222</v>
+        <v>282</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>160</v>
+        <v>191</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>35</v>
+        <v>192</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>36</v>
@@ -4370,27 +4350,27 @@
         <v>22</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="J74" s="3">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>194</v>
+        <v>155</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>195</v>
+        <v>35</v>
       </c>
       <c r="E75" s="3" t="s">
         <v>36</v>
@@ -4400,24 +4380,24 @@
         <v>22</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>39</v>
+        <v>284</v>
       </c>
       <c r="J75" s="3">
-        <v>22</v>
+        <v>61</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>182</v>
+        <v>297</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>131</v>
@@ -4430,174 +4410,174 @@
         <v>22</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>84</v>
+        <v>244</v>
       </c>
       <c r="J76" s="3">
-        <v>28</v>
+        <v>44</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C77" s="3" t="s">
         <v>301</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>284</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>131</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F77" s="3"/>
       <c r="G77" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>165</v>
+        <v>214</v>
       </c>
       <c r="J77" s="3">
-        <v>1</v>
+        <v>46</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="B78" s="3" t="s">
-        <v>305</v>
-      </c>
       <c r="C78" s="3" t="s">
-        <v>160</v>
+        <v>191</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>35</v>
+        <v>192</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F78" s="3"/>
       <c r="G78" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>307</v>
+        <v>281</v>
       </c>
       <c r="J78" s="3">
-        <v>88</v>
+        <v>42</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>309</v>
+        <v>275</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>160</v>
+        <v>276</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>35</v>
+        <v>131</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F79" s="3"/>
       <c r="G79" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>311</v>
+        <v>162</v>
       </c>
       <c r="J79" s="3">
-        <v>60</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>314</v>
+        <v>48</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F80" s="3"/>
       <c r="G80" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>238</v>
+        <v>175</v>
       </c>
       <c r="J80" s="3">
-        <v>43</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>182</v>
+        <v>264</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>131</v>
+        <v>312</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F81" s="3"/>
       <c r="G81" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>318</v>
+        <v>201</v>
       </c>
       <c r="J81" s="3">
-        <v>45</v>
+        <v>3</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>283</v>
+        <v>178</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>131</v>
@@ -4610,54 +4590,54 @@
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="J82" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>322</v>
+        <v>190</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>48</v>
+        <v>155</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F83" s="3"/>
       <c r="G83" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>169</v>
+        <v>318</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>35</v>
@@ -4670,27 +4650,27 @@
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>169</v>
+        <v>256</v>
       </c>
       <c r="J84" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>266</v>
+        <v>323</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>253</v>
+        <v>312</v>
       </c>
       <c r="E85" s="3" t="s">
         <v>36</v>
@@ -4700,32 +4680,34 @@
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>204</v>
+        <v>218</v>
       </c>
       <c r="J85" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>40</v>
+        <v>326</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>236</v>
+        <v>327</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>160</v>
+        <v>328</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>35</v>
+        <v>312</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F86" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>329</v>
+      </c>
       <c r="G86" s="3" t="s">
         <v>22</v>
       </c>
@@ -4733,97 +4715,101 @@
         <v>330</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>84</v>
+        <v>331</v>
       </c>
       <c r="J86" s="3">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F87" s="3"/>
+        <v>41</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>334</v>
+      </c>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>258</v>
+        <v>211</v>
       </c>
       <c r="J87" s="3">
-        <v>4</v>
+        <v>43</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E88" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F88" s="3"/>
+      <c r="F88" s="3" t="s">
+        <v>337</v>
+      </c>
       <c r="G88" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="J88" s="3">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>338</v>
+        <v>208</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>131</v>
+        <v>209</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>169</v>
+        <v>218</v>
       </c>
       <c r="J89" s="3">
         <v>0</v>
@@ -4831,107 +4817,105 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>340</v>
+        <v>66</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>251</v>
+        <v>343</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>252</v>
+        <v>155</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>253</v>
+        <v>35</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>343</v>
+        <v>281</v>
       </c>
       <c r="J90" s="3">
-        <v>25</v>
+        <v>42</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>40</v>
+        <v>345</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>344</v>
+        <v>229</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>194</v>
+        <v>155</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>195</v>
+        <v>35</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>120</v>
+        <v>347</v>
       </c>
       <c r="J91" s="3">
-        <v>38</v>
+        <v>15</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>348</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="F92" s="3"/>
       <c r="G92" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="J92" s="3">
-        <v>42</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>66</v>
+        <v>351</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>160</v>
+        <v>203</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>35</v>
@@ -4939,31 +4923,29 @@
       <c r="E93" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F93" s="3" t="s">
-        <v>351</v>
-      </c>
+      <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>289</v>
+        <v>165</v>
       </c>
       <c r="J93" s="3">
-        <v>41</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>222</v>
+        <v>170</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>35</v>
@@ -4976,107 +4958,17 @@
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>355</v>
+        <v>175</v>
       </c>
       <c r="J94" s="3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E95" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F95" s="3"/>
-      <c r="G95" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H95" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="I95" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="J95" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="C96" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F96" s="3"/>
-      <c r="G96" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="J96" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="B97" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C97" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E97" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F97" s="3"/>
-      <c r="G97" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="I97" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="J97" s="3">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J97"/>
+  <autoFilter ref="A1:J94"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5171,9 +5063,6 @@
     <hyperlink ref="H92" r:id="rId91"/>
     <hyperlink ref="H93" r:id="rId92"/>
     <hyperlink ref="H94" r:id="rId93"/>
-    <hyperlink ref="H95" r:id="rId94"/>
-    <hyperlink ref="H96" r:id="rId95"/>
-    <hyperlink ref="H97" r:id="rId96"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5181,8 +5070,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="1" max="1" width="56" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5215,13 +5104,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>166</v>
+        <v>215</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>167</v>
+        <v>216</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5229,18 +5118,18 @@
         <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>168</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>40</v>
+        <v>222</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>178</v>
+        <v>223</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5248,18 +5137,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>179</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>170</v>
+        <v>314</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>197</v>
+        <v>178</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>198</v>
+        <v>301</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5267,18 +5156,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>199</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>170</v>
+        <v>322</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>234</v>
+        <v>323</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>194</v>
+        <v>324</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5286,18 +5175,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>235</v>
+        <v>325</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>170</v>
+        <v>340</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>274</v>
+        <v>341</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>183</v>
+        <v>208</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5305,97 +5194,17 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>363</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G10"/>
+  <autoFilter ref="A1:G6"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
     <hyperlink ref="G4" r:id="rId3"/>
     <hyperlink ref="G5" r:id="rId4"/>
     <hyperlink ref="G6" r:id="rId5"/>
-    <hyperlink ref="G7" r:id="rId6"/>
-    <hyperlink ref="G8" r:id="rId7"/>
-    <hyperlink ref="G9" r:id="rId8"/>
-    <hyperlink ref="G10" r:id="rId9"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5409,15 +5218,15 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>366</v>
+        <v>337</v>
       </c>
       <c r="B2" s="3">
         <v>20</v>
@@ -5425,31 +5234,31 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="B4" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B5" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="B6" s="3">
         <v>13</v>
@@ -5457,15 +5266,15 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="B7" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="B8" s="3">
         <v>12</v>
@@ -5473,18 +5282,18 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B9" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -5497,7 +5306,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="B12" s="3">
         <v>9</v>
@@ -5505,7 +5314,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="B13" s="3">
         <v>8</v>
@@ -5513,7 +5322,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="B14" s="3">
         <v>7</v>
@@ -5521,15 +5330,15 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="B15" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -5551,7 +5360,7 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
     </row>
     <row r="2">
@@ -5572,10 +5381,10 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>167</v>
+        <v>190</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -5596,7 +5405,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5604,7 +5413,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -5612,7 +5421,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="B9" s="3">
         <v>3</v>
@@ -5636,7 +5445,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5644,7 +5453,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>236</v>
+        <v>264</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5652,7 +5461,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>251</v>
+        <v>275</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5660,7 +5469,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5668,10 +5477,10 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>283</v>
+        <v>47</v>
       </c>
       <c r="B16" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5682,23 +5491,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
     </row>
     <row r="2">
@@ -5762,13 +5571,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>53</v>
+        <v>190</v>
       </c>
       <c r="C6" s="3">
-        <v>5.0</v>
+        <v>6.6</v>
       </c>
       <c r="D6" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -5776,13 +5585,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>167</v>
+        <v>53</v>
       </c>
       <c r="C7" s="3">
-        <v>4.8</v>
+        <v>5.0</v>
       </c>
       <c r="D7" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -5804,7 +5613,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C9" s="3">
         <v>3.6</v>
@@ -5818,7 +5627,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C10" s="3">
         <v>3.6</v>
@@ -5832,7 +5641,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="C11" s="3">
         <v>3.6</v>
@@ -5860,10 +5669,10 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>251</v>
+        <v>282</v>
       </c>
       <c r="C13" s="3">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="D13" s="3">
         <v>2</v>
@@ -5874,13 +5683,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>236</v>
+        <v>136</v>
       </c>
       <c r="C14" s="3">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D14" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -5888,10 +5697,10 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C15" s="3">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="D15" s="3">
         <v>1</v>
@@ -5902,13 +5711,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>141</v>
+        <v>220</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
       </c>
       <c r="D16" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5928,21 +5737,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3">
@@ -5950,10 +5759,10 @@
         <v>36</v>
       </c>
       <c r="B3" s="3">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
     </row>
     <row r="4">
@@ -5964,7 +5773,7 @@
         <v>50</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -5983,7 +5792,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
     </row>
     <row r="2">
@@ -5991,7 +5800,7 @@
         <v>35</v>
       </c>
       <c r="B2" s="3">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3">
@@ -5999,20 +5808,20 @@
         <v>131</v>
       </c>
       <c r="B3" s="3">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B4" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>253</v>
+        <v>312</v>
       </c>
       <c r="B5" s="3">
         <v>3</v>
@@ -6020,15 +5829,15 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -6044,7 +5853,7 @@
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="4" max="4" width="42" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="60" customWidth="1"/>
@@ -6055,10 +5864,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>380</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>388</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -6070,10 +5879,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -6090,28 +5899,28 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>73</v>
@@ -6122,31 +5931,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4">
@@ -6154,28 +5963,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>80</v>
@@ -6186,28 +5995,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>80</v>
@@ -6218,31 +6027,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="F6" s="3">
         <v>80</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>416</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7">
@@ -6250,28 +6059,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>328</v>
+        <v>311</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="F7" s="3">
         <v>70</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="J7" s="3" t="s">
         <v>80</v>
@@ -6282,31 +6091,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="F8" s="3">
         <v>68</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>426</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9">
@@ -6314,28 +6123,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="F9" s="3">
         <v>61</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>65</v>
@@ -6346,31 +6155,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>264</v>
+        <v>424</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>394</v>
+        <v>420</v>
       </c>
       <c r="F10" s="3">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>73</v>
+        <v>331</v>
       </c>
     </row>
     <row r="11">
@@ -6378,31 +6187,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>206</v>
+        <v>429</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="F11" s="3">
         <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>343</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12">
@@ -6410,31 +6219,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>441</v>
+        <v>171</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="F12" s="3">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">
@@ -6442,31 +6251,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>445</v>
+        <v>438</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>446</v>
+        <v>386</v>
       </c>
       <c r="F13" s="3">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>51</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14">
@@ -6474,31 +6283,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>211</v>
+        <v>443</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="F14" s="3">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>117</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15">
@@ -6506,28 +6315,28 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>454</v>
+        <v>447</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="F15" s="3">
         <v>39</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>455</v>
+        <v>448</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>456</v>
+        <v>449</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>80</v>
@@ -6538,31 +6347,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="F16" s="3">
         <v>36</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="17">
@@ -6570,31 +6379,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>463</v>
+        <v>155</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="F17" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -6605,28 +6414,28 @@
         <v>457</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>160</v>
+        <v>208</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>394</v>
+        <v>420</v>
       </c>
       <c r="F18" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>80</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19">
@@ -6634,31 +6443,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>211</v>
+        <v>463</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="F19" s="3">
         <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>472</v>
+        <v>465</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>289</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20">
@@ -6666,28 +6475,28 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>322</v>
+        <v>308</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="F20" s="3">
         <v>24</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>474</v>
+        <v>467</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>475</v>
+        <v>468</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>39</v>
@@ -6698,31 +6507,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>476</v>
+        <v>282</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="F21" s="3">
         <v>24</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>153</v>
+        <v>472</v>
       </c>
     </row>
   </sheetData>

--- a/reports/devops-jobs-israel-2026-W39.xlsx
+++ b/reports/devops-jobs-israel-2026-W39.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="490">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="497">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -36,7 +36,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-25T11:41:46</t>
+    <t xml:space="preserve">2026-09-27T11:53:57</t>
   </si>
   <si>
     <t xml:space="preserve">Total open roles</t>
@@ -204,6 +204,18 @@
     <t xml:space="preserve">https://join.jfrog.com/job/?job=7434101&amp;gh_jid=7434101</t>
   </si>
   <si>
+    <t xml:space="preserve">Senior Software Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Docker, CI/CD, Python, Helm, Prometheus, Istio, MongoDB, Kafka, Security, Argo CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=7510102&amp;gh_jid=7510102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-10</t>
+  </si>
+  <si>
     <t xml:space="preserve">Developer Experience (DevEx) Team Lead</t>
   </si>
   <si>
@@ -456,6 +468,21 @@
     <t xml:space="preserve">https://www.transmitsecurity.com/about/careers/job?gh_jid=7945746002</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps Lead (FedRAMP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orcasecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">United States</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes, AWS, Azure, GCP, Terraform, CI/CD, Helm, Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://orca.security/about/careers/6149333004?gh_jid=6149333004</t>
+  </si>
+  <si>
     <t xml:space="preserve">Site Reliability Team Leader</t>
   </si>
   <si>
@@ -483,16 +510,19 @@
     <t xml:space="preserve">2026-09-07</t>
   </si>
   <si>
-    <t xml:space="preserve">Viz.ai</t>
+    <t xml:space="preserve">Principal DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
   </si>
   <si>
     <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-viz-ai-4449757750</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-07</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-at-palo-alto-networks-4469323268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-24</t>
   </si>
   <si>
     <t xml:space="preserve">Sr. Principal, DevOps</t>
@@ -522,6 +552,21 @@
     <t xml:space="preserve">DevOps Engineer</t>
   </si>
   <si>
+    <t xml:space="preserve">Echo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-echo-4459855925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal DevOps Engineer (Prisma Access Browser)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-devops-engineer-prisma-access-browser-at-palo-alto-networks-4441523866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
     <t xml:space="preserve">CommBox</t>
   </si>
   <si>
@@ -546,9 +591,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-play-perfect-4469727405</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24</t>
-  </si>
-  <si>
     <t xml:space="preserve">Nayax</t>
   </si>
   <si>
@@ -573,10 +615,13 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-engineer-devops-at-akamai-technologies-4461033122</t>
   </si>
   <si>
-    <t xml:space="preserve">Connecteam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-connecteam-4290904319</t>
+    <t xml:space="preserve">Transmit Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-transmit-security-4205225561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-16</t>
   </si>
   <si>
     <t xml:space="preserve">Pagaya</t>
@@ -588,10 +633,85 @@
     <t xml:space="preserve">2026-07-13</t>
   </si>
   <si>
-    <t xml:space="preserve">Senior DevOps Engineer (Secrets Manager)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Palo Alto Networks</t>
+    <t xml:space="preserve">Sela</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4469714710</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARAN Software</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aran-software-4470406189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FireArc Technologies .LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-firearc-technologies-ltd-4470443498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Akeyless Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4457183616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer Platform Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DriveNets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-platform-engineering-at-drivenets-4391719035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI First DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tomorrow.io</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-first-devops-engineer-at-tomorrow-io-4469679411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Engineer 4218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank Hapoalim בנק הפועלים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-4218-at-bank-hapoalim-%D7%91%D7%A0%D7%A7-%D7%94%D7%A4%D7%95%D7%A2%D7%9C%D7%99%D7%9D-4469435452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gloat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gloat-4471492397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cellebrite</t>
   </si>
   <si>
     <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
@@ -600,49 +720,349 @@
     <t xml:space="preserve">Petah Tikva</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-secrets-manager-at-palo-alto-networks-4419602029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sela</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sela-4469714710</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FireArc Technologies .LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-firearc-technologies-ltd-4470443498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARAN Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-aran-software-4470406189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Akeyless Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-akeyless-security-4457183616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior DevOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ethosia</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cellebrite-4469980397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assured Allies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-assured-allies-4468548060</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZyG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-zyg-4470271839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silverfort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platform DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-jeen-ai-4469586887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nanox Vision</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nanox-vision-4470995085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiverr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4451663128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dialog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4464714816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gotfriends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4464286063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Infra Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BioCatch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-infra-engineer-at-biocatch-4426796089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AllCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4470273860</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-confidential-careers-4468585946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SQLink Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lod, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4468557198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elbit Systems Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-elbit-systems-israel-4412297784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Engineer (1006977)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-1006977-at-elad-software-systems-4472440295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer 4210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-4210-at-bank-hapoalim-%D7%91%D7%A0%D7%A7-%D7%94%D7%A4%D7%95%D7%A2%D7%9C%D7%99%D7%9D-4469434426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oracle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441563717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior/Principal Site Reliability Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-site-reliability-engineer-at-palo-alto-networks-4470801230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VP, Site Reliability Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/vp-site-reliability-engineering-at-oracle-4459580128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manager, Production Engineering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crusoe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-production-engineering-at-crusoe-4442593613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRE Tech Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARMAN International</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-dt-4452913774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobgether</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-jobgether-4468496644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infrastructure Engineer (Kubernetes &amp; Node.js)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oriient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-kubernetes-node-js-at-oriient-4461069125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DevOps Data Infrastructure Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-team-leader-at-evoke-4470918616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-sqlink-group-4468564839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior Software and DevOps Engineer, DOCA Verification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-and-devops-engineer-doca-verification-at-nvidia-4404223687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps / Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blast Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-platform-engineer-at-blast-security-4470566478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head of DevOps &amp; Cloud Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nimble</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/head-of-devops-cloud-infrastructure-at-nimble-4450219176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Principal Platform Engineer - Devops (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-platform-engineer-devops-cortex-at-palo-alto-networks-4459956703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior DevOps Engineer - Backend Infrastructure Team (Cortex)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-backend-infrastructure-team-cortex-at-palo-alto-networks-4470803159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud and DevOps Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TeraCyte Analytics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ness Ziona, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-and-devops-engineer-at-teracyte-analytics-4470595912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Platform Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TAIRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4470554283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Engineer - Azure &amp; AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-azure-aws-at-elbit-systems-israel-4458838595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devops Cloud Team Lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genpact</t>
   </si>
   <si>
     <t xml:space="preserve">Netanya, Center District, Israel</t>
@@ -651,453 +1071,57 @@
     <t xml:space="preserve">Netanya</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-at-ethosia-4450151540</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-team-lead-at-genpact-4469756686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior MLOps Platform Engineer - QuantumBlack, AI by McKinsey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QuantumBlack, AI by McKinsey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI/MLOps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-mlops-platform-engineer-quantumblack-ai-by-mckinsey-at-quantumblack-ai-by-mckinsey-4423517900</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-13</t>
   </si>
   <si>
-    <t xml:space="preserve">Sr Staff DevOps Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sr-staff-devops-platform-engineer-at-palo-alto-networks-4419603015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI First DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tomorrow.io</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-first-devops-engineer-at-tomorrow-io-4469679411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer 4218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bank Hapoalim בנק הפועלים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-4218-at-bank-hapoalim-%D7%91%D7%A0%D7%A7-%D7%94%D7%A4%D7%95%D7%A2%D7%9C%D7%99%D7%9D-4469435452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gloat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gloat-4471492397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cellebrite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-cellebrite-4469980397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assured Allies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-assured-allies-4468548060</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paragon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-paragon-4400922396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZyG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-zyg-4470271839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Platform DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/platform-devops-engineer-at-jeen-ai-4469586887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silverfort</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-platform-engineer-at-silverfort-4442624759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nanox Vision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-nanox-vision-4470995085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiverr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-fiverr-4451663128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dialog</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-dialog-4464714816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gotfriends</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-gotfriends-4464286063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Engineer III</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CrowdStrike</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-iii-at-crowdstrike-4438706386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stealth Startup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-devops-engineer-at-stealth-startup-4468441366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AllCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-allcloud-4470273860</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-infrastructure-engineer-at-confidential-careers-4468585946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SQLink Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lod, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-engineer-at-sqlink-group-4468557198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Infrastructure Engineer 4210</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/infrastructure-engineer-4210-at-bank-hapoalim-%D7%91%D7%A0%D7%A7-%D7%94%D7%A4%D7%95%D7%A2%D7%9C%D7%99%D7%9D-4469434426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Tech Lead (BigBrain)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monday.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-tech-lead-bigbrain-at-monday-com-4451540255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior/Principal SRE Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-principal-sre-engineer-at-palo-alto-networks-4440426822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Site Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-jobgether-4468712370</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer - Algorithmic Trading</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DRW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-algorithmic-trading-at-drw-4414517115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Oracle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-site-reliability-engineer-at-oracle-4441563717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Platform Reliability Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IgniteTech</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-platform-reliability-engineer-at-ignitetech-4442432462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Site Reliability Engineer (SRE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/site-reliability-engineer-sre-at-paragon-4456184154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VP, Site Reliability Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/vp-site-reliability-engineering-at-oracle-4459580128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Manager, Production Engineering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Crusoe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/manager-production-engineering-at-crusoe-4442593613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SRE Tech Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HARMAN International</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/sre-tech-lead-at-harman-international-4452441331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Research-Ops &amp; DevOps Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-research-ops-devops-engineer-at-nvidia-4450945565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-dt-4452913774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-infrastructure-engineer-at-jobgether-4468496644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Data Infrastructure Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-data-infrastructure-team-leader-at-evoke-4470918616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-infrastructure-engineer-at-sqlink-group-4468564839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Software and DevOps Engineer, DOCA Verification</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-software-and-devops-engineer-doca-verification-at-nvidia-4404223687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Principal Platform Engineer - Devops (Cortex)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/principal-platform-engineer-devops-cortex-at-palo-alto-networks-4459956703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Research Infra Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dream</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/research-infra-engineer-at-dream-4370342612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI Platform Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TAIRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Or Akiva, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/ai-platform-engineer-at-tairc-4466990468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Engineer - Azure &amp; AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elbit Systems Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-engineer-azure-aws-at-elbit-systems-israel-4458838595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior MLOps Platform Engineer - QuantumBlack, AI by McKinsey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">QuantumBlack, AI by McKinsey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI/MLOps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-mlops-platform-engineer-quantumblack-ai-by-mckinsey-at-quantumblack-ai-by-mckinsey-4423517900</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior Staff DevOps Engineer - Cloud Security</t>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4468579109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senior IT System Administrator 243902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Experis Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-it-system-administrator-243902-at-experis-israel-4468981404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mentions</t>
   </si>
   <si>
     <t xml:space="preserve">Security</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-staff-devops-engineer-cloud-security-at-palo-alto-networks-4450813194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devops Cloud Team Lead</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genpact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-team-lead-at-genpact-4469756686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Semperis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-cloud-security-engineer-at-semperis-4438770193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft System Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COMDA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/microsoft-system-engineer-at-comda-4468579109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senior IT System Administrator 243902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Experis Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/senior-it-system-administrator-243902-at-experis-israel-4468981404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DevOps Deployment Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-deployment-engineer-at-jeen-ai-4471412751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mentions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
@@ -1110,27 +1134,27 @@
     <t xml:space="preserve">GCP</t>
   </si>
   <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform</t>
+  </si>
+  <si>
     <t xml:space="preserve">Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">Terraform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
     <t xml:space="preserve">Python</t>
   </si>
   <si>
+    <t xml:space="preserve">Helm</t>
+  </si>
+  <si>
     <t xml:space="preserve">Networking</t>
   </si>
   <si>
     <t xml:space="preserve">Argo CD</t>
   </si>
   <si>
-    <t xml:space="preserve">Helm</t>
-  </si>
-  <si>
     <t xml:space="preserve">WAF/CDN</t>
   </si>
   <si>
@@ -1155,10 +1179,10 @@
     <t xml:space="preserve">0%</t>
   </si>
   <si>
-    <t xml:space="preserve">46.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.8%</t>
+    <t xml:space="preserve">45.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.3%</t>
   </si>
   <si>
     <t xml:space="preserve">Role</t>
@@ -1272,9 +1296,6 @@
     <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
     <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
   </si>
   <si>
@@ -1428,16 +1449,16 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
   </si>
   <si>
-    <t xml:space="preserve">Systems Engineer 2, Technical Operations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/systems-engineer-2-technical-operations-at-oracle-4441078871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-16</t>
+    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
   </si>
   <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
@@ -1461,7 +1482,7 @@
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
-    <t xml:space="preserve">Virtualization</t>
+    <t xml:space="preserve">Git</t>
   </si>
   <si>
     <t xml:space="preserve">Elapsed (s)</t>
@@ -1613,7 +1634,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="7">
@@ -1621,7 +1642,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1629,7 +1650,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
@@ -1637,7 +1658,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>933</v>
+        <v>909</v>
       </c>
     </row>
     <row r="10">
@@ -1709,7 +1730,7 @@
         <v>22</v>
       </c>
       <c r="B19" s="3">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
@@ -1717,7 +1738,7 @@
         <v>23</v>
       </c>
       <c r="B20" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1736,12 +1757,12 @@
         <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="B2" s="3">
         <v>14</v>
@@ -1749,7 +1770,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="B3" s="3">
         <v>7</v>
@@ -1757,7 +1778,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="B4" s="3">
         <v>7</v>
@@ -1765,7 +1786,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="B5" s="3">
         <v>2</v>
@@ -1773,7 +1794,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1781,7 +1802,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -1800,23 +1821,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="B2" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="B3" s="3">
         <v>18</v>
@@ -1824,31 +1845,31 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="B4" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="B5" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="B6" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="B7" s="3">
         <v>12</v>
@@ -1856,7 +1877,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="B8" s="3">
         <v>11</v>
@@ -1864,7 +1885,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="B9" s="3">
         <v>9</v>
@@ -1872,7 +1893,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="B10" s="3">
         <v>8</v>
@@ -1880,7 +1901,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="B11" s="3">
         <v>7</v>
@@ -1888,7 +1909,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>358</v>
+        <v>313</v>
       </c>
       <c r="B12" s="3">
         <v>7</v>
@@ -1896,7 +1917,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="B13" s="3">
         <v>6</v>
@@ -1904,7 +1925,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="B14" s="3">
         <v>6</v>
@@ -1912,7 +1933,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="B15" s="3">
         <v>4</v>
@@ -1920,7 +1941,7 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="B16" s="3">
         <v>4</v>
@@ -1948,13 +1969,13 @@
         <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
     </row>
     <row r="2">
@@ -1962,13 +1983,13 @@
         <v>23</v>
       </c>
       <c r="B2" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C2" s="3">
-        <v>13.6</v>
+        <v>28.7</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="E2" s="3"/>
     </row>
@@ -1977,34 +1998,34 @@
         <v>22</v>
       </c>
       <c r="B3" s="3">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C3" s="3">
-        <v>35.7</v>
+        <v>34.7</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="B5" s="3">
         <v>0</v>
@@ -2013,52 +2034,52 @@
         <v>2.4</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="B6" s="3">
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="B7" s="3">
         <v>0</v>
       </c>
       <c r="C7" s="3">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="B8" s="3">
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>21.0</v>
+        <v>21.2</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2142,7 +2163,7 @@
         <v>39</v>
       </c>
       <c r="J2" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -2174,7 +2195,7 @@
         <v>44</v>
       </c>
       <c r="J3" s="3">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
@@ -2206,7 +2227,7 @@
         <v>44</v>
       </c>
       <c r="J4" s="3">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5">
@@ -2238,7 +2259,7 @@
         <v>51</v>
       </c>
       <c r="J5" s="3">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
@@ -2270,7 +2291,7 @@
         <v>57</v>
       </c>
       <c r="J6" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -2302,7 +2323,7 @@
         <v>44</v>
       </c>
       <c r="J7" s="3">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8">
@@ -2310,10 +2331,10 @@
         <v>61</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>35</v>
@@ -2322,27 +2343,27 @@
         <v>41</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="J8" s="3">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>35</v>
@@ -2366,7 +2387,7 @@
         <v>69</v>
       </c>
       <c r="J9" s="3">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
@@ -2374,7 +2395,7 @@
         <v>70</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>35</v>
@@ -2398,15 +2419,15 @@
         <v>73</v>
       </c>
       <c r="J10" s="3">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>35</v>
@@ -2418,27 +2439,27 @@
         <v>41</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J11" s="3">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>35</v>
@@ -2462,7 +2483,7 @@
         <v>80</v>
       </c>
       <c r="J12" s="3">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -2470,7 +2491,7 @@
         <v>81</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>35</v>
@@ -2494,7 +2515,7 @@
         <v>84</v>
       </c>
       <c r="J13" s="3">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -2502,7 +2523,7 @@
         <v>85</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>35</v>
@@ -2526,7 +2547,7 @@
         <v>88</v>
       </c>
       <c r="J14" s="3">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15">
@@ -2534,10 +2555,10 @@
         <v>89</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>35</v>
@@ -2546,30 +2567,30 @@
         <v>41</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="J15" s="3">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>91</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>35</v>
@@ -2590,7 +2611,7 @@
         <v>98</v>
       </c>
       <c r="J16" s="3">
-        <v>60</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -2598,16 +2619,16 @@
         <v>99</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>100</v>
@@ -2619,21 +2640,21 @@
         <v>101</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="J17" s="3">
-        <v>11</v>
+        <v>62</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>35</v>
@@ -2642,51 +2663,51 @@
         <v>36</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>57</v>
+        <v>92</v>
       </c>
       <c r="J18" s="3">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>108</v>
+        <v>57</v>
       </c>
       <c r="J19" s="3">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
@@ -2694,10 +2715,10 @@
         <v>109</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>35</v>
@@ -2706,19 +2727,19 @@
         <v>41</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H20" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="I20" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="J20" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -2726,10 +2747,10 @@
         <v>113</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>35</v>
@@ -2747,21 +2768,21 @@
         <v>116</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="J21" s="3">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>40</v>
+        <v>117</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>35</v>
+        <v>118</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>35</v>
@@ -2770,60 +2791,60 @@
         <v>41</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J22" s="3">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>121</v>
+        <v>40</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="G23" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="I23" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="J23" s="3">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="C24" s="3" t="s">
         <v>35</v>
       </c>
@@ -2831,97 +2852,97 @@
         <v>35</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>59</v>
+        <v>127</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J24" s="3">
-        <v>7</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>130</v>
+        <v>35</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>132</v>
+        <v>59</v>
       </c>
       <c r="G25" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="J25" s="3">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="E26" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="G26" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="I26" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="J26" s="3">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="C27" s="3" t="s">
-        <v>142</v>
+        <v>95</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>35</v>
@@ -2930,51 +2951,51 @@
         <v>41</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>44</v>
+        <v>143</v>
       </c>
       <c r="J27" s="3">
-        <v>45</v>
+        <v>54</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="D28" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>148</v>
+        <v>44</v>
       </c>
       <c r="J28" s="3">
-        <v>37</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29">
@@ -2985,49 +3006,51 @@
         <v>150</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>153</v>
+        <v>69</v>
       </c>
       <c r="J29" s="3">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>40</v>
+        <v>154</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>155</v>
+        <v>35</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F30" s="3"/>
+        <v>36</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>127</v>
+      </c>
       <c r="G30" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>156</v>
@@ -3036,7 +3059,7 @@
         <v>157</v>
       </c>
       <c r="J30" s="3">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31">
@@ -3047,17 +3070,19 @@
         <v>159</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="D31" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F31" s="3"/>
       <c r="G31" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>161</v>
@@ -3066,18 +3091,18 @@
         <v>162</v>
       </c>
       <c r="J31" s="3">
-        <v>4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>40</v>
+        <v>163</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>35</v>
@@ -3090,70 +3115,70 @@
         <v>22</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="J32" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>48</v>
+        <v>170</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="J33" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>169</v>
+        <v>40</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="J34" s="3">
         <v>4</v>
@@ -3161,43 +3186,43 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>40</v>
+        <v>176</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>175</v>
+        <v>112</v>
       </c>
       <c r="J35" s="3">
-        <v>1</v>
+        <v>30</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>40</v>
+        <v>179</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>48</v>
+        <v>165</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>35</v>
@@ -3210,147 +3235,147 @@
         <v>22</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="J36" s="3">
-        <v>2</v>
+        <v>23</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>40</v>
+        <v>176</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>179</v>
+        <v>48</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>44</v>
+        <v>175</v>
       </c>
       <c r="J37" s="3">
-        <v>45</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>155</v>
+        <v>186</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>65</v>
+        <v>172</v>
       </c>
       <c r="J38" s="3">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>166</v>
+        <v>40</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>108</v>
+        <v>167</v>
       </c>
       <c r="J39" s="3">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>166</v>
+        <v>40</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>155</v>
+        <v>48</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="J40" s="3">
-        <v>74</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>189</v>
+        <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>192</v>
+        <v>35</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>41</v>
@@ -3360,87 +3385,87 @@
         <v>22</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>157</v>
+        <v>44</v>
       </c>
       <c r="J41" s="3">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>166</v>
+        <v>195</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>195</v>
+        <v>165</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>175</v>
+        <v>69</v>
       </c>
       <c r="J42" s="3">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>48</v>
+        <v>165</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>165</v>
+        <v>200</v>
       </c>
       <c r="J43" s="3">
-        <v>2</v>
+        <v>42</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="E44" s="3" t="s">
         <v>36</v>
@@ -3450,174 +3475,174 @@
         <v>22</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="J44" s="3">
-        <v>3</v>
+        <v>76</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>40</v>
+        <v>176</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>205</v>
+        <v>167</v>
       </c>
       <c r="J45" s="3">
-        <v>31</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>206</v>
+        <v>176</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>207</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>209</v>
+        <v>135</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="J46" s="3">
-        <v>43</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>212</v>
+        <v>176</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>191</v>
+        <v>48</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>192</v>
+        <v>35</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>214</v>
+        <v>175</v>
       </c>
       <c r="J47" s="3">
-        <v>46</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>215</v>
+        <v>40</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>179</v>
+        <v>213</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="J48" s="3">
-        <v>0</v>
+        <v>33</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>165</v>
+        <v>219</v>
       </c>
       <c r="J49" s="3">
-        <v>2</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>155</v>
+        <v>193</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>35</v>
@@ -3630,30 +3655,30 @@
         <v>22</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="J50" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>40</v>
+        <v>224</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>225</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>192</v>
+        <v>35</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3" t="s">
@@ -3663,114 +3688,114 @@
         <v>226</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="J51" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>40</v>
+        <v>227</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>203</v>
+        <v>165</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="J52" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>166</v>
+        <v>40</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>155</v>
+        <v>231</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>35</v>
+        <v>232</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="J53" s="3">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>222</v>
+        <v>40</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>155</v>
+        <v>213</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F54" s="3"/>
       <c r="G54" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="J54" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>234</v>
+        <v>176</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>170</v>
+        <v>236</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="E55" s="3" t="s">
         <v>36</v>
@@ -3780,24 +3805,24 @@
         <v>22</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>162</v>
+        <v>238</v>
       </c>
       <c r="J55" s="3">
-        <v>4</v>
+        <v>34</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>35</v>
@@ -3810,27 +3835,27 @@
         <v>22</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>239</v>
+        <v>209</v>
       </c>
       <c r="J56" s="3">
-        <v>65</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>166</v>
+        <v>241</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>192</v>
+        <v>35</v>
       </c>
       <c r="E57" s="3" t="s">
         <v>36</v>
@@ -3840,27 +3865,27 @@
         <v>22</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>175</v>
+        <v>244</v>
       </c>
       <c r="J57" s="3">
-        <v>1</v>
+        <v>67</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>166</v>
+        <v>245</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>242</v>
+        <v>185</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>155</v>
+        <v>186</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>36</v>
@@ -3870,27 +3895,27 @@
         <v>22</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>244</v>
+        <v>172</v>
       </c>
       <c r="J58" s="3">
-        <v>44</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>171</v>
+        <v>231</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>131</v>
+        <v>232</v>
       </c>
       <c r="E59" s="3" t="s">
         <v>36</v>
@@ -3900,24 +3925,24 @@
         <v>22</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>247</v>
+        <v>167</v>
       </c>
       <c r="J59" s="3">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>35</v>
@@ -3930,27 +3955,27 @@
         <v>22</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="J60" s="3">
-        <v>12</v>
+        <v>46</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>250</v>
+        <v>176</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>155</v>
+        <v>186</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="E61" s="3" t="s">
         <v>36</v>
@@ -3960,87 +3985,87 @@
         <v>22</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J61" s="3">
-        <v>70</v>
+        <v>14</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>40</v>
+        <v>176</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>171</v>
+        <v>193</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F62" s="3"/>
       <c r="G62" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="J62" s="3">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>166</v>
+        <v>257</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>258</v>
+        <v>165</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>259</v>
+        <v>35</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F63" s="3"/>
       <c r="G63" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>201</v>
+        <v>64</v>
       </c>
       <c r="J63" s="3">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="C64" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="D64" s="3" t="s">
         <v>262</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="E64" s="3" t="s">
         <v>36</v>
@@ -4053,24 +4078,24 @@
         <v>263</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>165</v>
+        <v>209</v>
       </c>
       <c r="J64" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>166</v>
+        <v>264</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>265</v>
+        <v>186</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E65" s="3" t="s">
         <v>36</v>
@@ -4083,24 +4108,24 @@
         <v>266</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="J65" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="B66" s="3" t="s">
-        <v>220</v>
-      </c>
       <c r="C66" s="3" t="s">
-        <v>179</v>
+        <v>268</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="E66" s="3" t="s">
         <v>36</v>
@@ -4110,100 +4135,100 @@
         <v>22</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>165</v>
+        <v>209</v>
       </c>
       <c r="J66" s="3">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>270</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>155</v>
+        <v>271</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>35</v>
+        <v>272</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>44</v>
+        <v>274</v>
       </c>
       <c r="J67" s="3">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>190</v>
+        <v>276</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>155</v>
+        <v>186</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>239</v>
+        <v>278</v>
       </c>
       <c r="J68" s="3">
-        <v>65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>275</v>
+        <v>225</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>276</v>
+        <v>193</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="J69" s="3">
         <v>4</v>
@@ -4211,46 +4236,46 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>279</v>
+        <v>164</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F70" s="3"/>
       <c r="G70" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>281</v>
+        <v>244</v>
       </c>
       <c r="J70" s="3">
-        <v>42</v>
+        <v>67</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>191</v>
+        <v>231</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>192</v>
+        <v>232</v>
       </c>
       <c r="E71" s="3" t="s">
         <v>41</v>
@@ -4260,27 +4285,27 @@
         <v>22</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="J71" s="3">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>286</v>
+        <v>164</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>276</v>
+        <v>165</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>131</v>
+        <v>35</v>
       </c>
       <c r="E72" s="3" t="s">
         <v>41</v>
@@ -4290,13 +4315,13 @@
         <v>22</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="J72" s="3">
-        <v>68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4304,10 +4329,10 @@
         <v>289</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>35</v>
@@ -4323,10 +4348,10 @@
         <v>290</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="J73" s="3">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="74">
@@ -4334,13 +4359,13 @@
         <v>291</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>191</v>
+        <v>231</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>192</v>
+        <v>232</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>36</v>
@@ -4356,7 +4381,7 @@
         <v>39</v>
       </c>
       <c r="J74" s="3">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="75">
@@ -4367,7 +4392,7 @@
         <v>294</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>35</v>
@@ -4383,10 +4408,10 @@
         <v>295</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="J75" s="3">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="76">
@@ -4400,7 +4425,7 @@
         <v>298</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E76" s="3" t="s">
         <v>41</v>
@@ -4413,10 +4438,10 @@
         <v>299</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="J76" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="77">
@@ -4424,13 +4449,13 @@
         <v>300</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>301</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E77" s="3" t="s">
         <v>41</v>
@@ -4443,24 +4468,24 @@
         <v>302</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>214</v>
+        <v>303</v>
       </c>
       <c r="J77" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>191</v>
+        <v>231</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>192</v>
+        <v>232</v>
       </c>
       <c r="E78" s="3" t="s">
         <v>41</v>
@@ -4470,27 +4495,27 @@
         <v>22</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>281</v>
+        <v>307</v>
       </c>
       <c r="J78" s="3">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>275</v>
+        <v>308</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E79" s="3" t="s">
         <v>41</v>
@@ -4500,24 +4525,24 @@
         <v>22</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="J79" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>48</v>
+        <v>193</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>35</v>
@@ -4525,32 +4550,34 @@
       <c r="E80" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F80" s="3"/>
+      <c r="F80" s="3" t="s">
+        <v>313</v>
+      </c>
       <c r="G80" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>175</v>
+        <v>69</v>
       </c>
       <c r="J80" s="3">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>264</v>
+        <v>316</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>311</v>
+        <v>48</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>312</v>
+        <v>35</v>
       </c>
       <c r="E81" s="3" t="s">
         <v>36</v>
@@ -4560,10 +4587,10 @@
         <v>22</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>201</v>
+        <v>167</v>
       </c>
       <c r="J81" s="3">
         <v>3</v>
@@ -4571,46 +4598,46 @@
     </row>
     <row r="82">
       <c r="A82" s="3" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>178</v>
+        <v>267</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>131</v>
+        <v>272</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F82" s="3"/>
       <c r="G82" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="J82" s="3">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>155</v>
+        <v>301</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>41</v>
@@ -4620,70 +4647,70 @@
         <v>22</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>318</v>
+        <v>223</v>
       </c>
       <c r="J83" s="3">
-        <v>22</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>155</v>
+        <v>193</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F84" s="3"/>
       <c r="G84" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="J84" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>324</v>
+        <v>165</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>312</v>
+        <v>35</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F85" s="3"/>
       <c r="G85" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>218</v>
+        <v>278</v>
       </c>
       <c r="J85" s="3">
         <v>0</v>
@@ -4691,23 +4718,21 @@
     </row>
     <row r="86">
       <c r="A86" s="3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>327</v>
+        <v>164</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>328</v>
+        <v>165</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>312</v>
+        <v>35</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>329</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="F86" s="3"/>
       <c r="G86" s="3" t="s">
         <v>22</v>
       </c>
@@ -4718,7 +4743,7 @@
         <v>331</v>
       </c>
       <c r="J86" s="3">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="87">
@@ -4726,10 +4751,10 @@
         <v>332</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>333</v>
+        <v>164</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>35</v>
@@ -4737,79 +4762,75 @@
       <c r="E87" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F87" s="3" t="s">
-        <v>334</v>
-      </c>
+      <c r="F87" s="3"/>
       <c r="G87" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>211</v>
+        <v>278</v>
       </c>
       <c r="J87" s="3">
-        <v>43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C88" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="B88" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>191</v>
-      </c>
       <c r="D88" s="3" t="s">
-        <v>192</v>
+        <v>135</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F88" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F88" s="3"/>
+      <c r="G88" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H88" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="G88" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H88" s="3" t="s">
-        <v>338</v>
-      </c>
       <c r="I88" s="3" t="s">
-        <v>339</v>
+        <v>278</v>
       </c>
       <c r="J88" s="3">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C89" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="B89" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>208</v>
-      </c>
       <c r="D89" s="3" t="s">
-        <v>209</v>
+        <v>272</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F89" s="3"/>
       <c r="G89" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>218</v>
+        <v>278</v>
       </c>
       <c r="J89" s="3">
         <v>0</v>
@@ -4817,22 +4838,22 @@
     </row>
     <row r="90">
       <c r="A90" s="3" t="s">
-        <v>66</v>
+        <v>342</v>
       </c>
       <c r="B90" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F90" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="C90" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E90" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>337</v>
       </c>
       <c r="G90" s="3" t="s">
         <v>22</v>
@@ -4841,111 +4862,113 @@
         <v>344</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>281</v>
+        <v>345</v>
       </c>
       <c r="J90" s="3">
-        <v>42</v>
+        <v>28</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>229</v>
+        <v>347</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>155</v>
+        <v>348</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>35</v>
+        <v>349</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F91" s="3"/>
       <c r="G91" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>347</v>
+        <v>223</v>
       </c>
       <c r="J91" s="3">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F92" s="3"/>
+        <v>41</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>353</v>
+      </c>
       <c r="G92" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>201</v>
+        <v>355</v>
       </c>
       <c r="J92" s="3">
-        <v>3</v>
+        <v>45</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>352</v>
+        <v>236</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>203</v>
+        <v>165</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>35</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F93" s="3"/>
       <c r="G93" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>165</v>
+        <v>64</v>
       </c>
       <c r="J93" s="3">
-        <v>2</v>
+        <v>17</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>170</v>
+        <v>359</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>155</v>
+        <v>193</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>35</v>
@@ -4958,17 +4981,47 @@
         <v>22</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="I94" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="J94" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B95" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="I95" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="J94" s="3">
-        <v>1</v>
+      <c r="J95" s="3">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J94"/>
+  <autoFilter ref="A1:J95"/>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1"/>
     <hyperlink ref="H3" r:id="rId2"/>
@@ -5063,6 +5116,7 @@
     <hyperlink ref="H92" r:id="rId91"/>
     <hyperlink ref="H93" r:id="rId92"/>
     <hyperlink ref="H94" r:id="rId93"/>
+    <hyperlink ref="H95" r:id="rId94"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5070,8 +5124,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
@@ -5104,13 +5158,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>215</v>
+        <v>275</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>216</v>
+        <v>276</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -5118,18 +5172,18 @@
         <v>22</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>217</v>
+        <v>277</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>222</v>
+        <v>287</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>223</v>
+        <v>164</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -5137,18 +5191,18 @@
         <v>22</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>224</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>178</v>
+        <v>324</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>301</v>
+        <v>193</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
@@ -5156,18 +5210,18 @@
         <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>324</v>
+        <v>165</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
@@ -5175,18 +5229,18 @@
         <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>341</v>
+        <v>164</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>208</v>
+        <v>165</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -5194,17 +5248,57 @@
         <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>342</v>
+        <v>333</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G8"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1"/>
     <hyperlink ref="G3" r:id="rId2"/>
     <hyperlink ref="G4" r:id="rId3"/>
     <hyperlink ref="G5" r:id="rId4"/>
     <hyperlink ref="G6" r:id="rId5"/>
+    <hyperlink ref="G7" r:id="rId6"/>
+    <hyperlink ref="G8" r:id="rId7"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -5218,87 +5312,87 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>337</v>
+        <v>313</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="B3" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="B4" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="B5" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="B6" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="B7" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="B8" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="B9" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="B10" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B11" s="3">
         <v>11</v>
@@ -5306,15 +5400,15 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="B12" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="B13" s="3">
         <v>8</v>
@@ -5322,23 +5416,23 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="B14" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="B16" s="3">
         <v>6</v>
@@ -5360,12 +5454,12 @@
         <v>25</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B2" s="3">
         <v>7</v>
@@ -5373,15 +5467,15 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>90</v>
+        <v>164</v>
       </c>
       <c r="B3" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>190</v>
+        <v>94</v>
       </c>
       <c r="B4" s="3">
         <v>5</v>
@@ -5397,7 +5491,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="B6" s="3">
         <v>3</v>
@@ -5405,7 +5499,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>170</v>
+        <v>114</v>
       </c>
       <c r="B7" s="3">
         <v>3</v>
@@ -5413,7 +5507,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="B8" s="3">
         <v>3</v>
@@ -5421,7 +5515,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B9" s="3">
         <v>3</v>
@@ -5429,7 +5523,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>53</v>
+        <v>126</v>
       </c>
       <c r="B10" s="3">
         <v>2</v>
@@ -5437,7 +5531,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>122</v>
+        <v>185</v>
       </c>
       <c r="B11" s="3">
         <v>2</v>
@@ -5445,7 +5539,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="B12" s="3">
         <v>2</v>
@@ -5453,7 +5547,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B13" s="3">
         <v>2</v>
@@ -5461,7 +5555,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B14" s="3">
         <v>2</v>
@@ -5469,7 +5563,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B15" s="3">
         <v>2</v>
@@ -5491,23 +5585,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
     </row>
     <row r="2">
@@ -5515,7 +5609,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C2" s="3">
         <v>26.9</v>
@@ -5529,7 +5623,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C3" s="3">
         <v>23.8</v>
@@ -5557,7 +5651,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="C5" s="3">
         <v>10.1</v>
@@ -5571,13 +5665,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>190</v>
+        <v>114</v>
       </c>
       <c r="C6" s="3">
-        <v>6.6</v>
+        <v>10.1</v>
       </c>
       <c r="D6" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -5585,13 +5679,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>53</v>
+        <v>164</v>
       </c>
       <c r="C7" s="3">
-        <v>5.0</v>
+        <v>7.2</v>
       </c>
       <c r="D7" s="3">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -5599,7 +5693,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C8" s="3">
         <v>3.6</v>
@@ -5613,7 +5707,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>170</v>
+        <v>192</v>
       </c>
       <c r="C9" s="3">
         <v>3.6</v>
@@ -5627,7 +5721,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>178</v>
+        <v>236</v>
       </c>
       <c r="C10" s="3">
         <v>3.6</v>
@@ -5641,13 +5735,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>229</v>
+        <v>47</v>
       </c>
       <c r="C11" s="3">
-        <v>3.6</v>
+        <v>3.0</v>
       </c>
       <c r="D11" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -5655,13 +5749,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>47</v>
+        <v>270</v>
       </c>
       <c r="C12" s="3">
-        <v>3.0</v>
+        <v>2.9</v>
       </c>
       <c r="D12" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -5669,7 +5763,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C13" s="3">
         <v>2.8</v>
@@ -5683,7 +5777,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C14" s="3">
         <v>2.6</v>
@@ -5697,7 +5791,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C15" s="3">
         <v>2.4</v>
@@ -5711,7 +5805,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>220</v>
+        <v>185</v>
       </c>
       <c r="C16" s="3">
         <v>2.4</v>
@@ -5737,21 +5831,21 @@
         <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
     </row>
     <row r="3">
@@ -5762,7 +5856,7 @@
         <v>43</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
     </row>
     <row r="4">
@@ -5770,10 +5864,10 @@
         <v>41</v>
       </c>
       <c r="B4" s="3">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -5792,7 +5886,7 @@
         <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2">
@@ -5800,12 +5894,12 @@
         <v>35</v>
       </c>
       <c r="B2" s="3">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B3" s="3">
         <v>15</v>
@@ -5813,31 +5907,31 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>192</v>
+        <v>232</v>
       </c>
       <c r="B4" s="3">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>312</v>
+        <v>272</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>209</v>
+        <v>262</v>
       </c>
       <c r="B6" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>259</v>
+        <v>349</v>
       </c>
       <c r="B7" s="3">
         <v>1</v>
@@ -5864,10 +5958,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>25</v>
@@ -5879,10 +5973,10 @@
         <v>27</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>20</v>
@@ -5899,31 +5993,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3">
@@ -5931,31 +6025,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
     </row>
     <row r="4">
@@ -5963,31 +6057,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5">
@@ -5995,31 +6089,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="F5" s="3">
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6">
@@ -6027,31 +6121,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="F6" s="3">
         <v>80</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>339</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7">
@@ -6059,31 +6153,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="F7" s="3">
         <v>70</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="8">
@@ -6091,31 +6185,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="F8" s="3">
         <v>68</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>417</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9">
@@ -6123,31 +6217,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>419</v>
+        <v>426</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="F9" s="3">
         <v>61</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>421</v>
+        <v>428</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10">
@@ -6155,31 +6249,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="F10" s="3">
         <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>331</v>
+        <v>345</v>
       </c>
     </row>
     <row r="11">
@@ -6187,31 +6281,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>427</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>420</v>
       </c>
       <c r="F11" s="3">
         <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>430</v>
+        <v>437</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>431</v>
+        <v>438</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12">
@@ -6219,28 +6313,28 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>432</v>
+        <v>439</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="F12" s="3">
         <v>46</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>51</v>
@@ -6251,31 +6345,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>208</v>
+        <v>348</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="F13" s="3">
         <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>439</v>
+        <v>446</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6283,31 +6377,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>441</v>
+        <v>448</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="F14" s="3">
         <v>40</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>445</v>
+        <v>452</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15">
@@ -6315,31 +6409,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>446</v>
+        <v>453</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="F15" s="3">
         <v>39</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>449</v>
+        <v>456</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="16">
@@ -6347,31 +6441,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="F16" s="3">
         <v>36</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
     </row>
     <row r="17">
@@ -6379,31 +6473,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="F17" s="3">
         <v>28</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="18">
@@ -6411,31 +6505,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>208</v>
+        <v>348</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="F18" s="3">
         <v>27</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>281</v>
+        <v>307</v>
       </c>
     </row>
     <row r="19">
@@ -6443,31 +6537,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="F19" s="3">
         <v>27</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20">
@@ -6475,28 +6569,28 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>48</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="F20" s="3">
         <v>24</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>39</v>
@@ -6507,31 +6601,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>282</v>
+        <v>477</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>386</v>
+        <v>427</v>
       </c>
       <c r="F21" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>472</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
